--- a/AIFirst實作課程/第1個app/商務報價單範本.xlsx
+++ b/AIFirst實作課程/第1個app/商務報價單範本.xlsx
@@ -1,19 +1,41 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <bookViews>
+    <workbookView xWindow="0" yWindow="40" windowWidth="15960" windowHeight="18080"/>
+  </bookViews>
   <sheets>
-    <sheet sheetId="1" name="商務報價單" state="visible" r:id="rId4"/>
+    <sheet name="商務報價單" sheetId="1" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="48">
-  <si>
-    <t xml:space="preserve">❖
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="47">
+  <si>
+    <t>❖
 ACME CORP
 智慧科技</t>
   </si>
@@ -124,9 +146,6 @@
   </si>
   <si>
     <t>銷售額合計 (未稅 Subtotal)</t>
-  </si>
-  <si>
-    <t/>
   </si>
   <si>
     <t>加值型營業稅 (VAT 5%)</t>
@@ -166,103 +185,99 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="NT$ #,##0"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="2">
+    <numFmt numFmtId="0" formatCode="General"/>
+    <numFmt numFmtId="59" formatCode="&quot;NT&quot;[$&quot;NT$&quot;]&quot; &quot;#,##0"/>
   </numFmts>
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="17">
     <font>
-      <color theme="1"/>
-      <family val="2"/>
-      <scheme val="minor"/>
       <sz val="11"/>
+      <color indexed="8"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <b/>
-      <color rgb="FF1E293B"/>
       <sz val="12"/>
+      <color indexed="8"/>
+      <name val="Helvetica Neue"/>
+    </font>
+    <font>
+      <sz val="15"/>
+      <color indexed="8"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color indexed="11"/>
       <name val="Microsoft JhengHei"/>
     </font>
     <font>
-      <b/>
-      <color rgb="FF0F172A"/>
       <sz val="18"/>
+      <color indexed="13"/>
       <name val="Microsoft JhengHei"/>
     </font>
     <font>
-      <color rgb="FF64748B"/>
       <sz val="10"/>
+      <color indexed="15"/>
       <name val="Microsoft JhengHei"/>
     </font>
     <font>
-      <b/>
-      <color rgb="FF334155"/>
       <sz val="10"/>
+      <color indexed="16"/>
       <name val="Microsoft JhengHei"/>
     </font>
     <font>
-      <b/>
-      <color rgb="FF1E293B"/>
       <sz val="10"/>
-      <name val="Microsoft JhengHei"/>
-    </font>
-    <font>
-      <color rgb="FF334155"/>
-      <sz val="9"/>
-      <name val="Microsoft JhengHei"/>
-    </font>
-    <font>
-      <b/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="10"/>
+      <color indexed="11"/>
       <name val="Microsoft JhengHei"/>
     </font>
     <font>
       <sz val="9"/>
+      <color indexed="16"/>
       <name val="Microsoft JhengHei"/>
     </font>
     <font>
-      <b/>
-      <color rgb="FF334155"/>
-      <sz val="9"/>
+      <sz val="10"/>
+      <color indexed="14"/>
       <name val="Microsoft JhengHei"/>
     </font>
     <font>
-      <b/>
-      <sz val="10"/>
+      <sz val="9"/>
+      <color indexed="8"/>
       <name val="Microsoft JhengHei"/>
     </font>
     <font>
-      <b/>
-      <color rgb="FF0F172A"/>
-      <sz val="11"/>
+      <sz val="10"/>
+      <color indexed="8"/>
       <name val="Microsoft JhengHei"/>
     </font>
     <font>
-      <b/>
-      <color rgb="FF1E3A8A"/>
-      <sz val="12"/>
+      <sz val="11"/>
+      <color indexed="13"/>
       <name val="Microsoft JhengHei"/>
     </font>
     <font>
-      <color rgb="FF64748B"/>
-      <sz val="9"/>
+      <sz val="12"/>
+      <color indexed="19"/>
       <name val="Microsoft JhengHei"/>
     </font>
     <font>
-      <b/>
-      <color rgb="FF475569"/>
       <sz val="9"/>
+      <color indexed="15"/>
       <name val="Microsoft JhengHei"/>
     </font>
     <font>
-      <color rgb="FF94A3B8"/>
+      <sz val="9"/>
+      <color indexed="20"/>
+      <name val="Microsoft JhengHei"/>
+    </font>
+    <font>
       <sz val="8"/>
+      <color indexed="21"/>
       <name val="Microsoft JhengHei"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -271,26 +286,36 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF1F5F9"/>
+        <fgColor indexed="12"/>
+        <bgColor auto="1"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE2E8F0"/>
+        <fgColor indexed="14"/>
+        <bgColor auto="1"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF1E293B"/>
+        <fgColor indexed="17"/>
+        <bgColor auto="1"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF8FAFC"/>
+        <fgColor indexed="11"/>
+        <bgColor auto="1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="18"/>
+        <bgColor auto="1"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -300,101 +325,270 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFCBD5E1"/>
+        <color indexed="9"/>
       </left>
       <right style="thin">
-        <color rgb="FFCBD5E1"/>
+        <color indexed="9"/>
       </right>
       <top style="thin">
-        <color rgb="FFCBD5E1"/>
+        <color indexed="9"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFCBD5E1"/>
+        <color indexed="10"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFCBD5E1"/>
+        <color indexed="9"/>
       </left>
       <right style="thin">
-        <color rgb="FFCBD5E1"/>
+        <color indexed="9"/>
       </right>
       <top style="thin">
-        <color rgb="FFCBD5E1"/>
+        <color indexed="9"/>
       </top>
-      <bottom style="double">
-        <color rgb="FF1E293B"/>
+      <bottom style="thin">
+        <color indexed="9"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="10"/>
+      </left>
+      <right style="thin">
+        <color indexed="10"/>
+      </right>
+      <top style="thin">
+        <color indexed="10"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="10"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="10"/>
+      </left>
+      <right style="thin">
+        <color indexed="9"/>
+      </right>
+      <top style="thin">
+        <color indexed="9"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="9"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="9"/>
+      </left>
+      <right style="thin">
+        <color indexed="9"/>
+      </right>
+      <top style="thin">
+        <color indexed="10"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="10"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="10"/>
+      </left>
+      <right style="thin">
+        <color indexed="10"/>
+      </right>
+      <top style="thin">
+        <color indexed="9"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="9"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="10"/>
+      </left>
+      <right style="thin">
+        <color indexed="10"/>
+      </right>
+      <top style="thin">
+        <color indexed="10"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="11"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="9"/>
+      </left>
+      <right style="thin">
+        <color indexed="9"/>
+      </right>
+      <top style="thin">
+        <color indexed="11"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="9"/>
       </bottom>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="26">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+  <cellXfs count="47">
+    <xf numFmtId="0" fontId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" borderId="1" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" borderId="2" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="3" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="3" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="3" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" borderId="5" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="4" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="3" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" borderId="6" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" borderId="3" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="5" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="10" fillId="3" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="10" fillId="3" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="10" fillId="3" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="59" fontId="10" fillId="3" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="10" fillId="6" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="8" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="10" fillId="6" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="10" fillId="6" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="59" fontId="10" fillId="6" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="8" fillId="3" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="3" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" borderId="3" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="59" fontId="11" fillId="3" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="12" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="12" fillId="4" borderId="7" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="7" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="59" fontId="13" fillId="4" borderId="7" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" borderId="8" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" borderId="2" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" borderId="2" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="49" fontId="14" borderId="2" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" borderId="2" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="49" fontId="15" fillId="6" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="3" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="16" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="49" fontId="16" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" borderId="3" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
   </cellXfs>
@@ -402,33 +596,51 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <tableStyles count="0"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="ff000000"/>
+      <rgbColor rgb="ffffffff"/>
+      <rgbColor rgb="ffff0000"/>
+      <rgbColor rgb="ff00ff00"/>
+      <rgbColor rgb="ff0000ff"/>
+      <rgbColor rgb="ffffff00"/>
+      <rgbColor rgb="ffff00ff"/>
+      <rgbColor rgb="ff00ffff"/>
+      <rgbColor rgb="ff000000"/>
+      <rgbColor rgb="ffaaaaaa"/>
+      <rgbColor rgb="ffcbd5e1"/>
+      <rgbColor rgb="ff1e293b"/>
+      <rgbColor rgb="fff1f5f9"/>
+      <rgbColor rgb="ff0f172a"/>
+      <rgbColor rgb="ffffffff"/>
+      <rgbColor rgb="ff64748b"/>
+      <rgbColor rgb="ff334155"/>
+      <rgbColor rgb="ffe2e8f0"/>
+      <rgbColor rgb="fff8fafc"/>
+      <rgbColor rgb="ff1e3a8a"/>
+      <rgbColor rgb="ff475569"/>
+      <rgbColor rgb="ff94a3b8"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office Theme">
       <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
+        <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1F497D"/>
+        <a:srgbClr val="A7A7A7"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="EEECE1"/>
+        <a:srgbClr val="535353"/>
       </a:lt2>
       <a:accent1>
         <a:srgbClr val="4F81BD"/>
@@ -452,82 +664,22 @@
         <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="800080"/>
+        <a:srgbClr val="FF00FF"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office Theme">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:latin typeface="Helvetica Neue"/>
+        <a:ea typeface="Helvetica Neue"/>
+        <a:cs typeface="Helvetica Neue"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:latin typeface="Helvetica Neue"/>
+        <a:ea typeface="Helvetica Neue"/>
+        <a:cs typeface="Helvetica Neue"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office Theme">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -561,7 +713,7 @@
               <a:schemeClr val="phClr">
                 <a:tint val="100000"/>
                 <a:shade val="100000"/>
-                <a:satMod val="130000"/>
+                <a:satMod val="129999"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
@@ -580,7 +732,7 @@
           <a:solidFill>
             <a:schemeClr val="phClr">
               <a:shade val="95000"/>
-              <a:satMod val="105000"/>
+              <a:satMod val="104999"/>
             </a:schemeClr>
           </a:solidFill>
           <a:prstDash val="solid"/>
@@ -601,16 +753,7 @@
       <a:effectStyleLst>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+            <a:outerShdw sx="100000" sy="100000" kx="0" ky="0" algn="b" rotWithShape="0" blurRad="38100" dist="23000" dir="5400000">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -619,23 +762,21 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+            <a:outerShdw sx="100000" sy="100000" kx="0" ky="0" algn="b" rotWithShape="0" blurRad="38100" dist="23000" dir="5400000">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw sx="100000" sy="100000" kx="0" ky="0" algn="b" rotWithShape="0" blurRad="38100" dist="20000" dir="5400000">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
@@ -692,434 +833,1288 @@
   </a:themeElements>
   <a:objectDefaults>
     <a:spDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
+      <a:spPr>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="25400" cap="flat">
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:round/>
+        </a:ln>
+        <a:effectLst>
+          <a:outerShdw sx="100000" sy="100000" kx="0" ky="0" algn="b" rotWithShape="0" blurRad="38100" dist="23000" dir="5400000">
+            <a:srgbClr val="000000">
+              <a:alpha val="35000"/>
+            </a:srgbClr>
+          </a:outerShdw>
+        </a:effectLst>
+        <a:sp3d/>
+      </a:spPr>
+      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="45719" tIns="45719" rIns="45719" bIns="45719" numCol="1" spcCol="38100" rtlCol="0" anchor="ctr" upright="0">
+        <a:spAutoFit/>
+      </a:bodyPr>
+      <a:lstStyle>
+        <a:defPPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" rtl="0" fontAlgn="auto" latinLnBrk="0" hangingPunct="0">
+          <a:lnSpc>
+            <a:spcPct val="100000"/>
+          </a:lnSpc>
+          <a:spcBef>
+            <a:spcPts val="0"/>
+          </a:spcBef>
+          <a:spcAft>
+            <a:spcPts val="0"/>
+          </a:spcAft>
+          <a:buClrTx/>
+          <a:buSzTx/>
+          <a:buFontTx/>
+          <a:buNone/>
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1100" u="none" kumimoji="0" normalizeH="0">
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:uFillTx/>
+            <a:latin typeface="Calibri"/>
+            <a:ea typeface="Calibri"/>
+            <a:cs typeface="Calibri"/>
+            <a:sym typeface="Calibri"/>
+          </a:defRPr>
+        </a:defPPr>
+        <a:lvl1pPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" rtl="0" fontAlgn="auto" latinLnBrk="1" hangingPunct="0">
+          <a:lnSpc>
+            <a:spcPct val="100000"/>
+          </a:lnSpc>
+          <a:spcBef>
+            <a:spcPts val="0"/>
+          </a:spcBef>
+          <a:spcAft>
+            <a:spcPts val="0"/>
+          </a:spcAft>
+          <a:buClrTx/>
+          <a:buSzTx/>
+          <a:buFontTx/>
+          <a:buNone/>
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:uFillTx/>
+          </a:defRPr>
+        </a:lvl1pPr>
+        <a:lvl2pPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" rtl="0" fontAlgn="auto" latinLnBrk="1" hangingPunct="0">
+          <a:lnSpc>
+            <a:spcPct val="100000"/>
+          </a:lnSpc>
+          <a:spcBef>
+            <a:spcPts val="0"/>
+          </a:spcBef>
+          <a:spcAft>
+            <a:spcPts val="0"/>
+          </a:spcAft>
+          <a:buClrTx/>
+          <a:buSzTx/>
+          <a:buFontTx/>
+          <a:buNone/>
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:uFillTx/>
+          </a:defRPr>
+        </a:lvl2pPr>
+        <a:lvl3pPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" rtl="0" fontAlgn="auto" latinLnBrk="1" hangingPunct="0">
+          <a:lnSpc>
+            <a:spcPct val="100000"/>
+          </a:lnSpc>
+          <a:spcBef>
+            <a:spcPts val="0"/>
+          </a:spcBef>
+          <a:spcAft>
+            <a:spcPts val="0"/>
+          </a:spcAft>
+          <a:buClrTx/>
+          <a:buSzTx/>
+          <a:buFontTx/>
+          <a:buNone/>
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:uFillTx/>
+          </a:defRPr>
+        </a:lvl3pPr>
+        <a:lvl4pPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" rtl="0" fontAlgn="auto" latinLnBrk="1" hangingPunct="0">
+          <a:lnSpc>
+            <a:spcPct val="100000"/>
+          </a:lnSpc>
+          <a:spcBef>
+            <a:spcPts val="0"/>
+          </a:spcBef>
+          <a:spcAft>
+            <a:spcPts val="0"/>
+          </a:spcAft>
+          <a:buClrTx/>
+          <a:buSzTx/>
+          <a:buFontTx/>
+          <a:buNone/>
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:uFillTx/>
+          </a:defRPr>
+        </a:lvl4pPr>
+        <a:lvl5pPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" rtl="0" fontAlgn="auto" latinLnBrk="1" hangingPunct="0">
+          <a:lnSpc>
+            <a:spcPct val="100000"/>
+          </a:lnSpc>
+          <a:spcBef>
+            <a:spcPts val="0"/>
+          </a:spcBef>
+          <a:spcAft>
+            <a:spcPts val="0"/>
+          </a:spcAft>
+          <a:buClrTx/>
+          <a:buSzTx/>
+          <a:buFontTx/>
+          <a:buNone/>
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:uFillTx/>
+          </a:defRPr>
+        </a:lvl5pPr>
+        <a:lvl6pPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" rtl="0" fontAlgn="auto" latinLnBrk="1" hangingPunct="0">
+          <a:lnSpc>
+            <a:spcPct val="100000"/>
+          </a:lnSpc>
+          <a:spcBef>
+            <a:spcPts val="0"/>
+          </a:spcBef>
+          <a:spcAft>
+            <a:spcPts val="0"/>
+          </a:spcAft>
+          <a:buClrTx/>
+          <a:buSzTx/>
+          <a:buFontTx/>
+          <a:buNone/>
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:uFillTx/>
+          </a:defRPr>
+        </a:lvl6pPr>
+        <a:lvl7pPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" rtl="0" fontAlgn="auto" latinLnBrk="1" hangingPunct="0">
+          <a:lnSpc>
+            <a:spcPct val="100000"/>
+          </a:lnSpc>
+          <a:spcBef>
+            <a:spcPts val="0"/>
+          </a:spcBef>
+          <a:spcAft>
+            <a:spcPts val="0"/>
+          </a:spcAft>
+          <a:buClrTx/>
+          <a:buSzTx/>
+          <a:buFontTx/>
+          <a:buNone/>
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:uFillTx/>
+          </a:defRPr>
+        </a:lvl7pPr>
+        <a:lvl8pPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" rtl="0" fontAlgn="auto" latinLnBrk="1" hangingPunct="0">
+          <a:lnSpc>
+            <a:spcPct val="100000"/>
+          </a:lnSpc>
+          <a:spcBef>
+            <a:spcPts val="0"/>
+          </a:spcBef>
+          <a:spcAft>
+            <a:spcPts val="0"/>
+          </a:spcAft>
+          <a:buClrTx/>
+          <a:buSzTx/>
+          <a:buFontTx/>
+          <a:buNone/>
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:uFillTx/>
+          </a:defRPr>
+        </a:lvl8pPr>
+        <a:lvl9pPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" rtl="0" fontAlgn="auto" latinLnBrk="1" hangingPunct="0">
+          <a:lnSpc>
+            <a:spcPct val="100000"/>
+          </a:lnSpc>
+          <a:spcBef>
+            <a:spcPts val="0"/>
+          </a:spcBef>
+          <a:spcAft>
+            <a:spcPts val="0"/>
+          </a:spcAft>
+          <a:buClrTx/>
+          <a:buSzTx/>
+          <a:buFontTx/>
+          <a:buNone/>
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:uFillTx/>
+          </a:defRPr>
+        </a:lvl9pPr>
+      </a:lstStyle>
       <a:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="3">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
+        <a:lnRef idx="0"/>
+        <a:fillRef idx="0"/>
+        <a:effectRef idx="0"/>
+        <a:fontRef idx="none"/>
       </a:style>
     </a:spDef>
     <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
+      <a:spPr>
+        <a:noFill/>
+        <a:ln w="25400" cap="flat">
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:round/>
+        </a:ln>
+        <a:effectLst>
+          <a:outerShdw sx="100000" sy="100000" kx="0" ky="0" algn="b" rotWithShape="0" blurRad="38100" dist="20000" dir="5400000">
+            <a:srgbClr val="000000">
+              <a:alpha val="38000"/>
+            </a:srgbClr>
+          </a:outerShdw>
+        </a:effectLst>
+        <a:sp3d/>
+      </a:spPr>
+      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="91439" tIns="45719" rIns="91439" bIns="45719" numCol="1" spcCol="38100" rtlCol="0" anchor="t" upright="0">
+        <a:noAutofit/>
+      </a:bodyPr>
+      <a:lstStyle>
+        <a:defPPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" rtl="0" fontAlgn="auto" latinLnBrk="1" hangingPunct="0">
+          <a:lnSpc>
+            <a:spcPct val="100000"/>
+          </a:lnSpc>
+          <a:spcBef>
+            <a:spcPts val="0"/>
+          </a:spcBef>
+          <a:spcAft>
+            <a:spcPts val="0"/>
+          </a:spcAft>
+          <a:buClrTx/>
+          <a:buSzTx/>
+          <a:buFontTx/>
+          <a:buNone/>
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:uFillTx/>
+          </a:defRPr>
+        </a:defPPr>
+        <a:lvl1pPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" rtl="0" fontAlgn="auto" latinLnBrk="1" hangingPunct="0">
+          <a:lnSpc>
+            <a:spcPct val="100000"/>
+          </a:lnSpc>
+          <a:spcBef>
+            <a:spcPts val="0"/>
+          </a:spcBef>
+          <a:spcAft>
+            <a:spcPts val="0"/>
+          </a:spcAft>
+          <a:buClrTx/>
+          <a:buSzTx/>
+          <a:buFontTx/>
+          <a:buNone/>
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:uFillTx/>
+          </a:defRPr>
+        </a:lvl1pPr>
+        <a:lvl2pPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" rtl="0" fontAlgn="auto" latinLnBrk="1" hangingPunct="0">
+          <a:lnSpc>
+            <a:spcPct val="100000"/>
+          </a:lnSpc>
+          <a:spcBef>
+            <a:spcPts val="0"/>
+          </a:spcBef>
+          <a:spcAft>
+            <a:spcPts val="0"/>
+          </a:spcAft>
+          <a:buClrTx/>
+          <a:buSzTx/>
+          <a:buFontTx/>
+          <a:buNone/>
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:uFillTx/>
+          </a:defRPr>
+        </a:lvl2pPr>
+        <a:lvl3pPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" rtl="0" fontAlgn="auto" latinLnBrk="1" hangingPunct="0">
+          <a:lnSpc>
+            <a:spcPct val="100000"/>
+          </a:lnSpc>
+          <a:spcBef>
+            <a:spcPts val="0"/>
+          </a:spcBef>
+          <a:spcAft>
+            <a:spcPts val="0"/>
+          </a:spcAft>
+          <a:buClrTx/>
+          <a:buSzTx/>
+          <a:buFontTx/>
+          <a:buNone/>
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:uFillTx/>
+          </a:defRPr>
+        </a:lvl3pPr>
+        <a:lvl4pPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" rtl="0" fontAlgn="auto" latinLnBrk="1" hangingPunct="0">
+          <a:lnSpc>
+            <a:spcPct val="100000"/>
+          </a:lnSpc>
+          <a:spcBef>
+            <a:spcPts val="0"/>
+          </a:spcBef>
+          <a:spcAft>
+            <a:spcPts val="0"/>
+          </a:spcAft>
+          <a:buClrTx/>
+          <a:buSzTx/>
+          <a:buFontTx/>
+          <a:buNone/>
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:uFillTx/>
+          </a:defRPr>
+        </a:lvl4pPr>
+        <a:lvl5pPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" rtl="0" fontAlgn="auto" latinLnBrk="1" hangingPunct="0">
+          <a:lnSpc>
+            <a:spcPct val="100000"/>
+          </a:lnSpc>
+          <a:spcBef>
+            <a:spcPts val="0"/>
+          </a:spcBef>
+          <a:spcAft>
+            <a:spcPts val="0"/>
+          </a:spcAft>
+          <a:buClrTx/>
+          <a:buSzTx/>
+          <a:buFontTx/>
+          <a:buNone/>
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:uFillTx/>
+          </a:defRPr>
+        </a:lvl5pPr>
+        <a:lvl6pPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" rtl="0" fontAlgn="auto" latinLnBrk="1" hangingPunct="0">
+          <a:lnSpc>
+            <a:spcPct val="100000"/>
+          </a:lnSpc>
+          <a:spcBef>
+            <a:spcPts val="0"/>
+          </a:spcBef>
+          <a:spcAft>
+            <a:spcPts val="0"/>
+          </a:spcAft>
+          <a:buClrTx/>
+          <a:buSzTx/>
+          <a:buFontTx/>
+          <a:buNone/>
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:uFillTx/>
+          </a:defRPr>
+        </a:lvl6pPr>
+        <a:lvl7pPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" rtl="0" fontAlgn="auto" latinLnBrk="1" hangingPunct="0">
+          <a:lnSpc>
+            <a:spcPct val="100000"/>
+          </a:lnSpc>
+          <a:spcBef>
+            <a:spcPts val="0"/>
+          </a:spcBef>
+          <a:spcAft>
+            <a:spcPts val="0"/>
+          </a:spcAft>
+          <a:buClrTx/>
+          <a:buSzTx/>
+          <a:buFontTx/>
+          <a:buNone/>
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:uFillTx/>
+          </a:defRPr>
+        </a:lvl7pPr>
+        <a:lvl8pPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" rtl="0" fontAlgn="auto" latinLnBrk="1" hangingPunct="0">
+          <a:lnSpc>
+            <a:spcPct val="100000"/>
+          </a:lnSpc>
+          <a:spcBef>
+            <a:spcPts val="0"/>
+          </a:spcBef>
+          <a:spcAft>
+            <a:spcPts val="0"/>
+          </a:spcAft>
+          <a:buClrTx/>
+          <a:buSzTx/>
+          <a:buFontTx/>
+          <a:buNone/>
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:uFillTx/>
+          </a:defRPr>
+        </a:lvl8pPr>
+        <a:lvl9pPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" rtl="0" fontAlgn="auto" latinLnBrk="1" hangingPunct="0">
+          <a:lnSpc>
+            <a:spcPct val="100000"/>
+          </a:lnSpc>
+          <a:spcBef>
+            <a:spcPts val="0"/>
+          </a:spcBef>
+          <a:spcAft>
+            <a:spcPts val="0"/>
+          </a:spcAft>
+          <a:buClrTx/>
+          <a:buSzTx/>
+          <a:buFontTx/>
+          <a:buNone/>
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:uFillTx/>
+          </a:defRPr>
+        </a:lvl9pPr>
+      </a:lstStyle>
       <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
+        <a:lnRef idx="0"/>
+        <a:fillRef idx="0"/>
+        <a:effectRef idx="0"/>
+        <a:fontRef idx="none"/>
       </a:style>
     </a:lnDef>
+    <a:txDef>
+      <a:spPr>
+        <a:noFill/>
+        <a:ln w="12700" cap="flat">
+          <a:noFill/>
+          <a:miter lim="400000"/>
+        </a:ln>
+        <a:effectLst/>
+        <a:sp3d/>
+      </a:spPr>
+      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="45719" tIns="45719" rIns="45719" bIns="45719" numCol="1" spcCol="38100" rtlCol="0" anchor="t" upright="0">
+        <a:spAutoFit/>
+      </a:bodyPr>
+      <a:lstStyle>
+        <a:defPPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" rtl="0" fontAlgn="auto" latinLnBrk="0" hangingPunct="0">
+          <a:lnSpc>
+            <a:spcPct val="100000"/>
+          </a:lnSpc>
+          <a:spcBef>
+            <a:spcPts val="0"/>
+          </a:spcBef>
+          <a:spcAft>
+            <a:spcPts val="0"/>
+          </a:spcAft>
+          <a:buClrTx/>
+          <a:buSzTx/>
+          <a:buFontTx/>
+          <a:buNone/>
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1100" u="none" kumimoji="0" normalizeH="0">
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:uFillTx/>
+            <a:latin typeface="Calibri"/>
+            <a:ea typeface="Calibri"/>
+            <a:cs typeface="Calibri"/>
+            <a:sym typeface="Calibri"/>
+          </a:defRPr>
+        </a:defPPr>
+        <a:lvl1pPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" rtl="0" fontAlgn="auto" latinLnBrk="1" hangingPunct="0">
+          <a:lnSpc>
+            <a:spcPct val="100000"/>
+          </a:lnSpc>
+          <a:spcBef>
+            <a:spcPts val="0"/>
+          </a:spcBef>
+          <a:spcAft>
+            <a:spcPts val="0"/>
+          </a:spcAft>
+          <a:buClrTx/>
+          <a:buSzTx/>
+          <a:buFontTx/>
+          <a:buNone/>
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:uFillTx/>
+          </a:defRPr>
+        </a:lvl1pPr>
+        <a:lvl2pPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" rtl="0" fontAlgn="auto" latinLnBrk="1" hangingPunct="0">
+          <a:lnSpc>
+            <a:spcPct val="100000"/>
+          </a:lnSpc>
+          <a:spcBef>
+            <a:spcPts val="0"/>
+          </a:spcBef>
+          <a:spcAft>
+            <a:spcPts val="0"/>
+          </a:spcAft>
+          <a:buClrTx/>
+          <a:buSzTx/>
+          <a:buFontTx/>
+          <a:buNone/>
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:uFillTx/>
+          </a:defRPr>
+        </a:lvl2pPr>
+        <a:lvl3pPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" rtl="0" fontAlgn="auto" latinLnBrk="1" hangingPunct="0">
+          <a:lnSpc>
+            <a:spcPct val="100000"/>
+          </a:lnSpc>
+          <a:spcBef>
+            <a:spcPts val="0"/>
+          </a:spcBef>
+          <a:spcAft>
+            <a:spcPts val="0"/>
+          </a:spcAft>
+          <a:buClrTx/>
+          <a:buSzTx/>
+          <a:buFontTx/>
+          <a:buNone/>
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:uFillTx/>
+          </a:defRPr>
+        </a:lvl3pPr>
+        <a:lvl4pPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" rtl="0" fontAlgn="auto" latinLnBrk="1" hangingPunct="0">
+          <a:lnSpc>
+            <a:spcPct val="100000"/>
+          </a:lnSpc>
+          <a:spcBef>
+            <a:spcPts val="0"/>
+          </a:spcBef>
+          <a:spcAft>
+            <a:spcPts val="0"/>
+          </a:spcAft>
+          <a:buClrTx/>
+          <a:buSzTx/>
+          <a:buFontTx/>
+          <a:buNone/>
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:uFillTx/>
+          </a:defRPr>
+        </a:lvl4pPr>
+        <a:lvl5pPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" rtl="0" fontAlgn="auto" latinLnBrk="1" hangingPunct="0">
+          <a:lnSpc>
+            <a:spcPct val="100000"/>
+          </a:lnSpc>
+          <a:spcBef>
+            <a:spcPts val="0"/>
+          </a:spcBef>
+          <a:spcAft>
+            <a:spcPts val="0"/>
+          </a:spcAft>
+          <a:buClrTx/>
+          <a:buSzTx/>
+          <a:buFontTx/>
+          <a:buNone/>
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:uFillTx/>
+          </a:defRPr>
+        </a:lvl5pPr>
+        <a:lvl6pPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" rtl="0" fontAlgn="auto" latinLnBrk="1" hangingPunct="0">
+          <a:lnSpc>
+            <a:spcPct val="100000"/>
+          </a:lnSpc>
+          <a:spcBef>
+            <a:spcPts val="0"/>
+          </a:spcBef>
+          <a:spcAft>
+            <a:spcPts val="0"/>
+          </a:spcAft>
+          <a:buClrTx/>
+          <a:buSzTx/>
+          <a:buFontTx/>
+          <a:buNone/>
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:uFillTx/>
+          </a:defRPr>
+        </a:lvl6pPr>
+        <a:lvl7pPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" rtl="0" fontAlgn="auto" latinLnBrk="1" hangingPunct="0">
+          <a:lnSpc>
+            <a:spcPct val="100000"/>
+          </a:lnSpc>
+          <a:spcBef>
+            <a:spcPts val="0"/>
+          </a:spcBef>
+          <a:spcAft>
+            <a:spcPts val="0"/>
+          </a:spcAft>
+          <a:buClrTx/>
+          <a:buSzTx/>
+          <a:buFontTx/>
+          <a:buNone/>
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:uFillTx/>
+          </a:defRPr>
+        </a:lvl7pPr>
+        <a:lvl8pPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" rtl="0" fontAlgn="auto" latinLnBrk="1" hangingPunct="0">
+          <a:lnSpc>
+            <a:spcPct val="100000"/>
+          </a:lnSpc>
+          <a:spcBef>
+            <a:spcPts val="0"/>
+          </a:spcBef>
+          <a:spcAft>
+            <a:spcPts val="0"/>
+          </a:spcAft>
+          <a:buClrTx/>
+          <a:buSzTx/>
+          <a:buFontTx/>
+          <a:buNone/>
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:uFillTx/>
+          </a:defRPr>
+        </a:lvl8pPr>
+        <a:lvl9pPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" rtl="0" fontAlgn="auto" latinLnBrk="1" hangingPunct="0">
+          <a:lnSpc>
+            <a:spcPct val="100000"/>
+          </a:lnSpc>
+          <a:spcBef>
+            <a:spcPts val="0"/>
+          </a:spcBef>
+          <a:spcAft>
+            <a:spcPts val="0"/>
+          </a:spcAft>
+          <a:buClrTx/>
+          <a:buSzTx/>
+          <a:buFontTx/>
+          <a:buNone/>
+          <a:defRPr b="0" baseline="0" cap="none" i="0" spc="0" strike="noStrike" sz="1800" u="none" kumimoji="0" normalizeH="0">
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:solidFill>
+              <a:srgbClr val="000000"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:uFillTx/>
+          </a:defRPr>
+        </a:lvl9pPr>
+      </a:lstStyle>
+      <a:style>
+        <a:lnRef idx="0"/>
+        <a:fillRef idx="0"/>
+        <a:effectRef idx="0"/>
+        <a:fontRef idx="none"/>
+      </a:style>
+    </a:txDef>
   </a:objectDefaults>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:G30"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <dimension ref="A1:G30"/>
+  <sheetFormatPr defaultColWidth="8.83333" defaultRowHeight="15" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="8" customWidth="1"/>
-    <col min="2" max="2" width="22" customWidth="1"/>
-    <col min="3" max="3" width="30" customWidth="1"/>
-    <col min="4" max="4" width="10" customWidth="1"/>
-    <col min="5" max="5" width="8" customWidth="1"/>
-    <col min="6" max="6" width="15" customWidth="1"/>
-    <col min="7" max="7" width="16" customWidth="1"/>
+    <col min="1" max="1" width="8" style="1" customWidth="1"/>
+    <col min="2" max="2" width="22" style="1" customWidth="1"/>
+    <col min="3" max="3" width="30" style="1" customWidth="1"/>
+    <col min="4" max="4" width="10" style="1" customWidth="1"/>
+    <col min="5" max="5" width="8" style="1" customWidth="1"/>
+    <col min="6" max="6" width="15" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16" style="1" customWidth="1"/>
+    <col min="8" max="16384" width="8.85156" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
+    <row r="1" ht="13.55" customHeight="1">
+      <c r="A1" s="2"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+    </row>
+    <row r="2" ht="27" customHeight="1">
+      <c r="A2" t="s" s="4">
         <v>0</v>
       </c>
-      <c r="B2" s="1"/>
-      <c r="C2" s="2" t="s">
+      <c r="B2" s="5"/>
+      <c r="C2" t="s" s="6">
         <v>1</v>
       </c>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="1"/>
-      <c r="B3" s="1"/>
-      <c r="C3" s="3" t="s">
+      <c r="D2" s="7"/>
+      <c r="E2" s="7"/>
+      <c r="F2" s="7"/>
+      <c r="G2" s="7"/>
+    </row>
+    <row r="3" ht="17" customHeight="1">
+      <c r="A3" s="5"/>
+      <c r="B3" s="5"/>
+      <c r="C3" t="s" s="8">
         <v>2</v>
       </c>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3"/>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="1"/>
-      <c r="B4" s="1"/>
-      <c r="C4" s="4" t="s">
+      <c r="D3" s="9"/>
+      <c r="E3" s="9"/>
+      <c r="F3" s="9"/>
+      <c r="G3" s="9"/>
+    </row>
+    <row r="4" ht="17" customHeight="1">
+      <c r="A4" s="5"/>
+      <c r="B4" s="5"/>
+      <c r="C4" t="s" s="10">
         <v>3</v>
       </c>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
-      <c r="G4" s="4"/>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
+      <c r="D4" s="11"/>
+      <c r="E4" s="11"/>
+      <c r="F4" s="11"/>
+      <c r="G4" s="11"/>
+    </row>
+    <row r="5" ht="13.55" customHeight="1">
+      <c r="A5" s="12"/>
+      <c r="B5" s="12"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="3"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
+    </row>
+    <row r="6" ht="17" customHeight="1">
+      <c r="A6" t="s" s="13">
         <v>4</v>
       </c>
-      <c r="B6" s="5"/>
-      <c r="C6" s="5"/>
-      <c r="E6" s="5" t="s">
+      <c r="B6" s="14"/>
+      <c r="C6" s="14"/>
+      <c r="D6" s="15"/>
+      <c r="E6" t="s" s="13">
         <v>5</v>
       </c>
-      <c r="F6" s="5"/>
-      <c r="G6" s="5"/>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="6" t="s">
+      <c r="F6" s="14"/>
+      <c r="G6" s="14"/>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="s" s="16">
         <v>6</v>
       </c>
-      <c r="B7" s="6"/>
-      <c r="C7" s="6"/>
-      <c r="E7" s="6" t="s">
+      <c r="B7" s="17"/>
+      <c r="C7" s="17"/>
+      <c r="D7" s="15"/>
+      <c r="E7" t="s" s="16">
         <v>7</v>
       </c>
-      <c r="F7" s="6"/>
-      <c r="G7" s="6"/>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="6" t="s">
+      <c r="F7" s="17"/>
+      <c r="G7" s="17"/>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" t="s" s="16">
         <v>8</v>
       </c>
-      <c r="B8" s="6"/>
-      <c r="C8" s="6"/>
-      <c r="E8" s="6" t="s">
+      <c r="B8" s="17"/>
+      <c r="C8" s="17"/>
+      <c r="D8" s="15"/>
+      <c r="E8" t="s" s="16">
         <v>9</v>
       </c>
-      <c r="F8" s="6"/>
-      <c r="G8" s="6"/>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="6" t="s">
+      <c r="F8" s="17"/>
+      <c r="G8" s="17"/>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" t="s" s="16">
         <v>10</v>
       </c>
-      <c r="B9" s="6"/>
-      <c r="C9" s="6"/>
-      <c r="E9" s="6" t="s">
+      <c r="B9" s="17"/>
+      <c r="C9" s="17"/>
+      <c r="D9" s="15"/>
+      <c r="E9" t="s" s="16">
         <v>11</v>
       </c>
-      <c r="F9" s="6"/>
-      <c r="G9" s="6"/>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="6" t="s">
+      <c r="F9" s="17"/>
+      <c r="G9" s="17"/>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="s" s="16">
         <v>12</v>
       </c>
-      <c r="B10" s="6"/>
-      <c r="C10" s="6"/>
-      <c r="E10" s="6" t="s">
+      <c r="B10" s="17"/>
+      <c r="C10" s="17"/>
+      <c r="D10" s="15"/>
+      <c r="E10" t="s" s="16">
         <v>13</v>
       </c>
-      <c r="F10" s="6"/>
-      <c r="G10" s="6"/>
-    </row>
-    <row r="12" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="7" t="s">
+      <c r="F10" s="17"/>
+      <c r="G10" s="17"/>
+    </row>
+    <row r="11" ht="13.55" customHeight="1">
+      <c r="A11" s="12"/>
+      <c r="B11" s="12"/>
+      <c r="C11" s="12"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="12"/>
+      <c r="F11" s="12"/>
+      <c r="G11" s="12"/>
+    </row>
+    <row r="12" ht="24" customHeight="1">
+      <c r="A12" t="s" s="18">
         <v>14</v>
       </c>
-      <c r="B12" s="7" t="s">
+      <c r="B12" t="s" s="18">
         <v>15</v>
       </c>
-      <c r="C12" s="7" t="s">
+      <c r="C12" t="s" s="18">
         <v>16</v>
       </c>
-      <c r="D12" s="7" t="s">
+      <c r="D12" t="s" s="18">
         <v>17</v>
       </c>
-      <c r="E12" s="7" t="s">
+      <c r="E12" t="s" s="18">
         <v>18</v>
       </c>
-      <c r="F12" s="7" t="s">
+      <c r="F12" t="s" s="18">
         <v>19</v>
       </c>
-      <c r="G12" s="7" t="s">
+      <c r="G12" t="s" s="18">
         <v>20</v>
       </c>
     </row>
-    <row r="13" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="8">
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="19">
         <v>1</v>
       </c>
-      <c r="B13" s="9" t="s">
+      <c r="B13" t="s" s="20">
         <v>21</v>
       </c>
-      <c r="C13" s="9" t="s">
+      <c r="C13" t="s" s="20">
         <v>22</v>
       </c>
-      <c r="D13" s="10">
+      <c r="D13" s="21">
         <v>1</v>
       </c>
-      <c r="E13" s="8" t="s">
+      <c r="E13" t="s" s="22">
         <v>23</v>
       </c>
-      <c r="F13" s="11">
+      <c r="F13" s="23">
         <v>65000</v>
       </c>
-      <c r="G13" s="11">
-        <f>D13*F13</f>
+      <c r="G13" s="23" cm="1">
+        <f t="array" ref="G13">D13*F13</f>
         <v>65000</v>
       </c>
     </row>
-    <row r="14" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="12">
+    <row r="14" ht="22" customHeight="1">
+      <c r="A14" s="24">
         <v>2</v>
       </c>
-      <c r="B14" s="13" t="s">
+      <c r="B14" t="s" s="25">
         <v>24</v>
       </c>
-      <c r="C14" s="13" t="s">
+      <c r="C14" t="s" s="25">
         <v>25</v>
       </c>
-      <c r="D14" s="14">
+      <c r="D14" s="26">
         <v>1</v>
       </c>
-      <c r="E14" s="12" t="s">
+      <c r="E14" t="s" s="27">
         <v>26</v>
       </c>
-      <c r="F14" s="15">
+      <c r="F14" s="28">
         <v>38000</v>
       </c>
-      <c r="G14" s="15">
-        <f>D14*F14</f>
+      <c r="G14" s="28" cm="1">
+        <f t="array" ref="G14">D14*F14</f>
         <v>38000</v>
       </c>
     </row>
-    <row r="15" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="8">
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="19">
         <v>3</v>
       </c>
-      <c r="B15" s="9" t="s">
+      <c r="B15" t="s" s="20">
         <v>27</v>
       </c>
-      <c r="C15" s="9" t="s">
+      <c r="C15" t="s" s="20">
         <v>28</v>
       </c>
-      <c r="D15" s="10">
+      <c r="D15" s="21">
         <v>2</v>
       </c>
-      <c r="E15" s="8" t="s">
+      <c r="E15" t="s" s="22">
         <v>29</v>
       </c>
-      <c r="F15" s="11">
+      <c r="F15" s="23">
         <v>15000</v>
       </c>
-      <c r="G15" s="11">
-        <f>D15*F15</f>
+      <c r="G15" s="23" cm="1">
+        <f t="array" ref="G15">D15*F15</f>
         <v>30000</v>
       </c>
     </row>
-    <row r="16" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="12">
+    <row r="16" ht="22" customHeight="1">
+      <c r="A16" s="24">
         <v>4</v>
       </c>
-      <c r="B16" s="13" t="s">
+      <c r="B16" t="s" s="25">
         <v>30</v>
       </c>
-      <c r="C16" s="13" t="s">
+      <c r="C16" t="s" s="25">
         <v>31</v>
       </c>
-      <c r="D16" s="14">
+      <c r="D16" s="26">
         <v>1</v>
       </c>
-      <c r="E16" s="12" t="s">
+      <c r="E16" t="s" s="27">
         <v>32</v>
       </c>
-      <c r="F16" s="15">
+      <c r="F16" s="28">
         <v>12000</v>
       </c>
-      <c r="G16" s="15">
-        <f>D16*F16</f>
+      <c r="G16" s="28" cm="1">
+        <f t="array" ref="G16">D16*F16</f>
         <v>12000</v>
       </c>
     </row>
-    <row r="17" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="8">
+    <row r="17" ht="22" customHeight="1">
+      <c r="A17" s="19">
         <v>5</v>
       </c>
-      <c r="B17" s="9" t="s">
+      <c r="B17" t="s" s="20">
         <v>33</v>
       </c>
-      <c r="C17" s="9" t="s">
+      <c r="C17" t="s" s="20">
         <v>34</v>
       </c>
-      <c r="D17" s="10">
+      <c r="D17" s="21">
         <v>12</v>
       </c>
-      <c r="E17" s="8" t="s">
+      <c r="E17" t="s" s="22">
         <v>35</v>
       </c>
-      <c r="F17" s="11">
+      <c r="F17" s="23">
         <v>3000</v>
       </c>
-      <c r="G17" s="11">
-        <f>D17*F17</f>
+      <c r="G17" s="23" cm="1">
+        <f t="array" ref="G17">D17*F17</f>
         <v>36000</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="16" t="s">
+    <row r="18" ht="17" customHeight="1">
+      <c r="A18" t="s" s="29">
         <v>36</v>
       </c>
-      <c r="B18" s="16"/>
-      <c r="C18" s="16"/>
-      <c r="D18" s="16"/>
-      <c r="E18" s="16"/>
-      <c r="F18" s="17" t="s">
+      <c r="B18" s="30"/>
+      <c r="C18" s="30"/>
+      <c r="D18" s="30"/>
+      <c r="E18" s="30"/>
+      <c r="F18" s="31"/>
+      <c r="G18" s="32" cm="1">
+        <f t="array" ref="G18">SUM(G13:G17)</f>
+        <v>181000</v>
+      </c>
+    </row>
+    <row r="19" ht="17" customHeight="1">
+      <c r="A19" t="s" s="29">
         <v>37</v>
       </c>
-      <c r="G18" s="18">
-        <f>SUM(G13:G17)</f>
-        <v>181000</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="16" t="s">
+      <c r="B19" s="30"/>
+      <c r="C19" s="30"/>
+      <c r="D19" s="30"/>
+      <c r="E19" s="30"/>
+      <c r="F19" s="31"/>
+      <c r="G19" s="32" cm="1">
+        <f t="array" ref="G19">ROUND(G18*0.05,0)</f>
+        <v>9050</v>
+      </c>
+    </row>
+    <row r="20" ht="19" customHeight="1">
+      <c r="A20" t="s" s="33">
         <v>38</v>
       </c>
-      <c r="B19" s="16"/>
-      <c r="C19" s="16"/>
-      <c r="D19" s="16"/>
-      <c r="E19" s="16"/>
-      <c r="F19" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="G19" s="18">
-        <f>ROUND(G18*0.05, 0)</f>
-        <v>9050</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="19" t="s">
+      <c r="B20" s="34"/>
+      <c r="C20" s="34"/>
+      <c r="D20" s="34"/>
+      <c r="E20" s="34"/>
+      <c r="F20" s="35"/>
+      <c r="G20" s="36" cm="1">
+        <f t="array" ref="G20">G18+G19</f>
+        <v>190050</v>
+      </c>
+    </row>
+    <row r="21" ht="13.55" customHeight="1">
+      <c r="A21" s="37"/>
+      <c r="B21" s="37"/>
+      <c r="C21" s="37"/>
+      <c r="D21" s="37"/>
+      <c r="E21" s="37"/>
+      <c r="F21" s="37"/>
+      <c r="G21" s="37"/>
+    </row>
+    <row r="22" ht="17" customHeight="1">
+      <c r="A22" t="s" s="38">
         <v>39</v>
       </c>
-      <c r="B20" s="19"/>
-      <c r="C20" s="19"/>
-      <c r="D20" s="19"/>
-      <c r="E20" s="19"/>
-      <c r="F20" s="20" t="s">
-        <v>37</v>
-      </c>
-      <c r="G20" s="21">
-        <f>G18+G19</f>
-        <v>190050</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="22" t="s">
+      <c r="B22" s="39"/>
+      <c r="C22" s="39"/>
+      <c r="D22" s="39"/>
+      <c r="E22" s="39"/>
+      <c r="F22" s="39"/>
+      <c r="G22" s="39"/>
+    </row>
+    <row r="23" ht="15" customHeight="1">
+      <c r="A23" t="s" s="40">
         <v>40</v>
       </c>
-      <c r="B22" s="22"/>
-      <c r="C22" s="22"/>
-      <c r="D22" s="22"/>
-      <c r="E22" s="22"/>
-      <c r="F22" s="22"/>
-      <c r="G22" s="22"/>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="23" t="s">
+      <c r="B23" s="41"/>
+      <c r="C23" s="41"/>
+      <c r="D23" s="41"/>
+      <c r="E23" s="41"/>
+      <c r="F23" s="41"/>
+      <c r="G23" s="41"/>
+    </row>
+    <row r="24" ht="15" customHeight="1">
+      <c r="A24" t="s" s="40">
         <v>41</v>
       </c>
-      <c r="B23" s="23"/>
-      <c r="C23" s="23"/>
-      <c r="D23" s="23"/>
-      <c r="E23" s="23"/>
-      <c r="F23" s="23"/>
-      <c r="G23" s="23"/>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="23" t="s">
+      <c r="B24" s="41"/>
+      <c r="C24" s="41"/>
+      <c r="D24" s="41"/>
+      <c r="E24" s="41"/>
+      <c r="F24" s="41"/>
+      <c r="G24" s="41"/>
+    </row>
+    <row r="25" ht="15" customHeight="1">
+      <c r="A25" t="s" s="40">
         <v>42</v>
       </c>
-      <c r="B24" s="23"/>
-      <c r="C24" s="23"/>
-      <c r="D24" s="23"/>
-      <c r="E24" s="23"/>
-      <c r="F24" s="23"/>
-      <c r="G24" s="23"/>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="23" t="s">
+      <c r="B25" s="41"/>
+      <c r="C25" s="41"/>
+      <c r="D25" s="41"/>
+      <c r="E25" s="41"/>
+      <c r="F25" s="41"/>
+      <c r="G25" s="41"/>
+    </row>
+    <row r="26" ht="13.55" customHeight="1">
+      <c r="A26" s="2"/>
+      <c r="B26" s="2"/>
+      <c r="C26" s="2"/>
+      <c r="D26" s="3"/>
+      <c r="E26" s="2"/>
+      <c r="F26" s="2"/>
+      <c r="G26" s="2"/>
+    </row>
+    <row r="27" ht="15" customHeight="1">
+      <c r="A27" t="s" s="42">
         <v>43</v>
       </c>
-      <c r="B25" s="23"/>
-      <c r="C25" s="23"/>
-      <c r="D25" s="23"/>
-      <c r="E25" s="23"/>
-      <c r="F25" s="23"/>
-      <c r="G25" s="23"/>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" s="24" t="s">
+      <c r="B27" s="43"/>
+      <c r="C27" s="43"/>
+      <c r="D27" s="15"/>
+      <c r="E27" t="s" s="42">
         <v>44</v>
       </c>
-      <c r="B27" s="24"/>
-      <c r="C27" s="24"/>
-      <c r="E27" s="24" t="s">
+      <c r="F27" s="43"/>
+      <c r="G27" s="43"/>
+    </row>
+    <row r="28" ht="13.55" customHeight="1">
+      <c r="A28" t="s" s="45">
         <v>45</v>
       </c>
-      <c r="F27" s="24"/>
-      <c r="G27" s="24"/>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" s="25" t="s">
+      <c r="B28" s="46"/>
+      <c r="C28" s="46"/>
+      <c r="D28" s="15"/>
+      <c r="E28" t="s" s="45">
         <v>46</v>
       </c>
-      <c r="B28" s="25"/>
-      <c r="C28" s="25"/>
-      <c r="E28" s="25" t="s">
-        <v>47</v>
-      </c>
-      <c r="F28" s="25"/>
-      <c r="G28" s="25"/>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="25"/>
-      <c r="B29" s="25"/>
-      <c r="C29" s="25"/>
-      <c r="E29" s="25"/>
-      <c r="F29" s="25"/>
-      <c r="G29" s="25"/>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" s="25"/>
-      <c r="B30" s="25"/>
-      <c r="C30" s="25"/>
-      <c r="E30" s="25"/>
-      <c r="F30" s="25"/>
-      <c r="G30" s="25"/>
+      <c r="F28" s="46"/>
+      <c r="G28" s="46"/>
+    </row>
+    <row r="29" ht="13.55" customHeight="1">
+      <c r="A29" s="46"/>
+      <c r="B29" s="46"/>
+      <c r="C29" s="46"/>
+      <c r="D29" s="15"/>
+      <c r="E29" s="46"/>
+      <c r="F29" s="46"/>
+      <c r="G29" s="46"/>
+    </row>
+    <row r="30" ht="19.85" customHeight="1">
+      <c r="A30" s="46"/>
+      <c r="B30" s="46"/>
+      <c r="C30" s="46"/>
+      <c r="D30" s="15"/>
+      <c r="E30" s="46"/>
+      <c r="F30" s="46"/>
+      <c r="G30" s="46"/>
     </row>
   </sheetData>
   <mergeCells count="25">
@@ -1150,6 +2145,9 @@
     <mergeCell ref="E28:G30"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup firstPageNumber="1" fitToHeight="1" fitToWidth="1" scale="100" useFirstPageNumber="0" orientation="portrait" pageOrder="downThenOver"/>
+  <headerFooter>
+    <oddFooter>&amp;C&amp;"Helvetica Neue,Regular"&amp;12&amp;K000000&amp;P</oddFooter>
+  </headerFooter>
 </worksheet>
 </file>
--- a/AIFirst實作課程/第1個app/商務報價單範本.xlsx
+++ b/AIFirst實作課程/第1個app/商務報價單範本.xlsx
@@ -1,52 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="40" windowWidth="15960" windowHeight="18080"/>
   </bookViews>
   <sheets>
-    <sheet name="商務報價單" sheetId="1" r:id="rId5"/>
+    <sheet sheetId="1" name="商務報價單" state="visible" r:id="rId4"/>
   </sheets>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="47">
-  <si>
-    <t>❖
-ACME CORP
-智慧科技</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="46">
   <si>
     <t>商 務 報 價 單  /  QUOTATION</t>
   </si>
   <si>
-    <t>報價單號：QT-20260926-001    |    報價日期：2026-09-26    |    有效期限：30 天</t>
-  </si>
-  <si>
-    <t>專案名稱：企業數位轉型前端自動化與報價管理系統建置</t>
+    <t>報價單號：{{QUOTATION_NO | QT-20260926-001}}    |    報價日期：{{QUOTATION_DATE | 2026-09-26}}    |    有效期限：{{VALID_DAYS | 30 天}}</t>
+  </si>
+  <si>
+    <t>專案名稱：{{PROJECT_NAME | 企業數位轉型前端自動化與報價管理系統建置}}</t>
   </si>
   <si>
     <t>【 供應商資訊 (我方) 】</t>
@@ -55,28 +31,28 @@
     <t>【 客戶買受人資訊 】</t>
   </si>
   <si>
-    <t>公司名稱：星創智慧科技有限公司</t>
-  </si>
-  <si>
-    <t>客戶名稱：宏達數位傳媒行銷有限公司</t>
-  </si>
-  <si>
-    <t>統一編號：88889999</t>
-  </si>
-  <si>
-    <t>統一編號：12345678</t>
-  </si>
-  <si>
-    <t>聯絡電話：(02) 2345-6789</t>
-  </si>
-  <si>
-    <t>聯絡窗口：陳專案經理 (0912-345-678)</t>
-  </si>
-  <si>
-    <t>公司地址：台北市信義區信義路五段7號</t>
-  </si>
-  <si>
-    <t>通訊地址：台北市中山區南京東路二段100號</t>
+    <t>公司名稱：{{PROVIDER_NAME | 星創智慧科技有限公司}}</t>
+  </si>
+  <si>
+    <t>客戶名稱：{{CLIENT_NAME | 宏達數位傳媒行銷有限公司}}</t>
+  </si>
+  <si>
+    <t>統一編號：{{PROVIDER_TAX_ID | 88889999}}</t>
+  </si>
+  <si>
+    <t>統一編號：{{CLIENT_TAX_ID | 12345678}}</t>
+  </si>
+  <si>
+    <t>聯絡電話：{{PROVIDER_PHONE | (02) 2345-6789}}</t>
+  </si>
+  <si>
+    <t>聯絡窗口：{{CLIENT_CONTACT | 陳專案經理 (0912-345-678)}}</t>
+  </si>
+  <si>
+    <t>公司地址：{{PROVIDER_ADDRESS | 台北市信義區信義路五段7號}}</t>
+  </si>
+  <si>
+    <t>通訊地址：{{CLIENT_ADDRESS | 台北市中山區南京東路二段100號}}</t>
   </si>
   <si>
     <t>項次</t>
@@ -100,49 +76,49 @@
     <t>小計金額 (NTD)</t>
   </si>
   <si>
-    <t>企業官網響應式切版</t>
-  </si>
-  <si>
-    <t>React + TypeScript 現代化 RWD 視覺架構</t>
-  </si>
-  <si>
-    <t>專案</t>
-  </si>
-  <si>
-    <t>純前端 Excel 匯出模組</t>
-  </si>
-  <si>
-    <t>ExcelJS 樣式渲染、多格式相容與離線下載</t>
-  </si>
-  <si>
-    <t>套件</t>
-  </si>
-  <si>
-    <t>商務邏輯與表單運算</t>
-  </si>
-  <si>
-    <t>營業稅、千分位計算、動態增刪項目與防呆</t>
-  </si>
-  <si>
-    <t>式</t>
-  </si>
-  <si>
-    <t>系統教育訓練與交接</t>
-  </si>
-  <si>
-    <t>提供完整原始碼、操作手冊與 4 小時講師訓練</t>
-  </si>
-  <si>
-    <t>場次</t>
-  </si>
-  <si>
-    <t>首年維護與技術諮詢</t>
-  </si>
-  <si>
-    <t>日常功能保固、相依套件升級檢視與線上諮詢</t>
-  </si>
-  <si>
-    <t>個月</t>
+    <t>{{ITEM_1_NAME | 企業官網響應式切版}}</t>
+  </si>
+  <si>
+    <t>{{ITEM_1_DESC | React + TypeScript 現代化 RWD 視覺架構}}</t>
+  </si>
+  <si>
+    <t>{{ITEM_1_UNIT | 專案}}</t>
+  </si>
+  <si>
+    <t>{{ITEM_2_NAME | 純前端 Excel 匯出模組}}</t>
+  </si>
+  <si>
+    <t>{{ITEM_2_DESC | ExcelJS 樣式渲染、多格式相容與離線下載}}</t>
+  </si>
+  <si>
+    <t>{{ITEM_2_UNIT | 套件}}</t>
+  </si>
+  <si>
+    <t>{{ITEM_3_NAME | 商務邏輯與表單運算}}</t>
+  </si>
+  <si>
+    <t>{{ITEM_3_DESC | 營業稅、千分位計算、動態增刪項目與防呆}}</t>
+  </si>
+  <si>
+    <t>{{ITEM_3_UNIT | 式}}</t>
+  </si>
+  <si>
+    <t>{{ITEM_4_NAME | 系統教育訓練與交接}}</t>
+  </si>
+  <si>
+    <t>{{ITEM_4_DESC | 提供完整原始碼、操作手冊與 4 小時講師訓練}}</t>
+  </si>
+  <si>
+    <t>{{ITEM_4_UNIT | 場次}}</t>
+  </si>
+  <si>
+    <t>{{ITEM_5_NAME | 首年維護與技術諮詢}}</t>
+  </si>
+  <si>
+    <t>{{ITEM_5_DESC | 日常功能保固、相依套件升級檢視與線上諮詢}}</t>
+  </si>
+  <si>
+    <t>{{ITEM_5_UNIT | 個月}}</t>
   </si>
   <si>
     <t>銷售額合計 (未稅 Subtotal)</t>
@@ -157,13 +133,13 @@
     <t>【 交易條款與備註說明 】</t>
   </si>
   <si>
-    <t>1. 付款條件：本專案依階段請款，簽約訂金 30%、期中展示驗收 40%、上線結案驗收 30%。</t>
-  </si>
-  <si>
-    <t>2. 匯款專戶：玉山銀行 (808) 營業部  帳號：1234-567-890123  戶名：星創智慧科技有限公司</t>
-  </si>
-  <si>
-    <t>3. 有效天數：本報價單內容自開立日起 30 日內有效，若逾期未確認需重新評估報價。</t>
+    <t>1. 付款條件：{{PAYMENT_TERMS | 本專案依階段請款，簽約訂金 30%、期中展示驗收 40%、上線結案驗收 30%。}}</t>
+  </si>
+  <si>
+    <t>2. 匯款專戶：{{BANK_ACCOUNT | 玉山銀行 (808) 營業部  帳號：1234-567-890123  戶名：星創智慧科技有限公司}}</t>
+  </si>
+  <si>
+    <t>3. 有效天數：{{VALID_TERMS | 本報價單內容自開立日起 30 日內有效，若逾期未確認需重新評估報價。}}</t>
   </si>
   <si>
     <t>供應商確認簽章 (發票章 / 大小章)</t>
@@ -185,95 +161,91 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="0" formatCode="General"/>
-    <numFmt numFmtId="59" formatCode="&quot;NT&quot;[$&quot;NT$&quot;]&quot; &quot;#,##0"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="&quot;NT&quot;[$&quot;NT$&quot;]&quot; &quot;#,##0"/>
   </numFmts>
-  <fonts count="17">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
+      <color theme="1"/>
+      <family val="2"/>
+      <scheme val="minor"/>
       <sz val="11"/>
-      <color indexed="8"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <sz val="12"/>
       <color indexed="8"/>
-      <name val="Helvetica Neue"/>
-    </font>
-    <font>
-      <sz val="15"/>
-      <color indexed="8"/>
+      <sz val="11"/>
       <name val="Calibri"/>
     </font>
     <font>
+      <color indexed="11"/>
       <sz val="12"/>
-      <color indexed="11"/>
       <name val="Microsoft JhengHei"/>
     </font>
     <font>
+      <color indexed="13"/>
       <sz val="18"/>
-      <color indexed="13"/>
       <name val="Microsoft JhengHei"/>
     </font>
     <font>
+      <color indexed="15"/>
       <sz val="10"/>
-      <color indexed="15"/>
       <name val="Microsoft JhengHei"/>
     </font>
     <font>
+      <color indexed="16"/>
       <sz val="10"/>
-      <color indexed="16"/>
       <name val="Microsoft JhengHei"/>
     </font>
     <font>
+      <color indexed="11"/>
       <sz val="10"/>
-      <color indexed="11"/>
       <name val="Microsoft JhengHei"/>
     </font>
     <font>
+      <color indexed="16"/>
       <sz val="9"/>
-      <color indexed="16"/>
       <name val="Microsoft JhengHei"/>
     </font>
     <font>
+      <color indexed="14"/>
       <sz val="10"/>
-      <color indexed="14"/>
       <name val="Microsoft JhengHei"/>
     </font>
     <font>
+      <color indexed="8"/>
       <sz val="9"/>
-      <color indexed="8"/>
       <name val="Microsoft JhengHei"/>
     </font>
     <font>
+      <color indexed="8"/>
       <sz val="10"/>
-      <color indexed="8"/>
       <name val="Microsoft JhengHei"/>
     </font>
     <font>
+      <color indexed="13"/>
       <sz val="11"/>
-      <color indexed="13"/>
       <name val="Microsoft JhengHei"/>
     </font>
     <font>
+      <color indexed="19"/>
       <sz val="12"/>
-      <color indexed="19"/>
       <name val="Microsoft JhengHei"/>
     </font>
     <font>
+      <color indexed="15"/>
       <sz val="9"/>
-      <color indexed="15"/>
       <name val="Microsoft JhengHei"/>
     </font>
     <font>
+      <color indexed="20"/>
       <sz val="9"/>
-      <color indexed="20"/>
       <name val="Microsoft JhengHei"/>
     </font>
     <font>
+      <color indexed="21"/>
       <sz val="8"/>
-      <color indexed="21"/>
       <name val="Microsoft JhengHei"/>
     </font>
   </fonts>
@@ -287,31 +259,26 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor indexed="12"/>
-        <bgColor auto="1"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor indexed="14"/>
-        <bgColor auto="1"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor indexed="17"/>
-        <bgColor auto="1"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor indexed="11"/>
-        <bgColor auto="1"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor indexed="18"/>
-        <bgColor auto="1"/>
       </patternFill>
     </fill>
   </fills>
@@ -445,150 +412,143 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  </cellStyleXfs>
+  <cellXfs count="46">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="bottom"/>
     </xf>
-  </cellStyleXfs>
-  <cellXfs count="47">
-    <xf numFmtId="0" fontId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="0" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="0" borderId="1" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="0" borderId="2" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="6" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="3" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="3" fontId="9" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="3" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="3" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" borderId="5" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="3" fontId="9" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="4" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="164" fontId="10" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="3" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="164" fontId="12" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="0" borderId="6" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="49" fontId="8" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="8" borderId="3" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="49" fontId="9" fillId="5" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="49" fontId="14" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="10" fillId="3" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="10" fillId="3" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="3" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="59" fontId="10" fillId="3" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="6" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="10" fillId="6" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="6" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="59" fontId="10" fillId="6" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="3" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="3" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" borderId="3" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="59" fontId="11" fillId="3" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="4" borderId="7" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="7" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="59" fontId="13" fillId="4" borderId="7" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" borderId="8" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" borderId="2" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" borderId="2" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="49" fontId="14" borderId="2" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" borderId="2" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="49" fontId="15" fillId="6" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="3" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="16" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="49" fontId="16" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="15" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="bottom" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" borderId="3" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
   </cellXfs>
@@ -596,34 +556,65 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="ff000000"/>
-      <rgbColor rgb="ffffffff"/>
-      <rgbColor rgb="ffff0000"/>
-      <rgbColor rgb="ff00ff00"/>
-      <rgbColor rgb="ff0000ff"/>
-      <rgbColor rgb="ffffff00"/>
-      <rgbColor rgb="ffff00ff"/>
-      <rgbColor rgb="ff00ffff"/>
-      <rgbColor rgb="ff000000"/>
-      <rgbColor rgb="ffaaaaaa"/>
-      <rgbColor rgb="ffcbd5e1"/>
-      <rgbColor rgb="ff1e293b"/>
-      <rgbColor rgb="fff1f5f9"/>
-      <rgbColor rgb="ff0f172a"/>
-      <rgbColor rgb="ffffffff"/>
-      <rgbColor rgb="ff64748b"/>
-      <rgbColor rgb="ff334155"/>
-      <rgbColor rgb="ffe2e8f0"/>
-      <rgbColor rgb="fff8fafc"/>
-      <rgbColor rgb="ff1e3a8a"/>
-      <rgbColor rgb="ff475569"/>
-      <rgbColor rgb="ff94a3b8"/>
-    </indexedColors>
-  </colors>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>12000</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>40499</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>187000</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>144500</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="0" cy="0"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1681,12 +1672,12 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G30"/>
-  <sheetFormatPr defaultColWidth="8.83333" defaultRowHeight="15" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.83333"/>
   <cols>
     <col min="1" max="1" width="8" style="1" customWidth="1"/>
     <col min="2" max="2" width="22" style="1" customWidth="1"/>
@@ -1698,7 +1689,7 @@
     <col min="8" max="16384" width="8.85156" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="13.55" customHeight="1">
+    <row r="1" ht="13.55" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="2"/>
       <c r="B1" s="2"/>
       <c r="C1" s="3"/>
@@ -1707,42 +1698,40 @@
       <c r="F1" s="3"/>
       <c r="G1" s="3"/>
     </row>
-    <row r="2" ht="27" customHeight="1">
-      <c r="A2" t="s" s="4">
+    <row r="2" ht="27" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" s="4"/>
+      <c r="B2" s="5"/>
+      <c r="C2" s="6" t="s">
         <v>0</v>
-      </c>
-      <c r="B2" s="5"/>
-      <c r="C2" t="s" s="6">
-        <v>1</v>
       </c>
       <c r="D2" s="7"/>
       <c r="E2" s="7"/>
       <c r="F2" s="7"/>
       <c r="G2" s="7"/>
     </row>
-    <row r="3" ht="17" customHeight="1">
+    <row r="3" ht="17" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="5"/>
       <c r="B3" s="5"/>
-      <c r="C3" t="s" s="8">
-        <v>2</v>
+      <c r="C3" s="8" t="s">
+        <v>1</v>
       </c>
       <c r="D3" s="9"/>
       <c r="E3" s="9"/>
       <c r="F3" s="9"/>
       <c r="G3" s="9"/>
     </row>
-    <row r="4" ht="17" customHeight="1">
+    <row r="4" ht="17" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="5"/>
       <c r="B4" s="5"/>
-      <c r="C4" t="s" s="10">
-        <v>3</v>
+      <c r="C4" s="10" t="s">
+        <v>2</v>
       </c>
       <c r="D4" s="11"/>
       <c r="E4" s="11"/>
       <c r="F4" s="11"/>
       <c r="G4" s="11"/>
     </row>
-    <row r="5" ht="13.55" customHeight="1">
+    <row r="5" ht="13.55" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="12"/>
       <c r="B5" s="12"/>
       <c r="C5" s="2"/>
@@ -1751,72 +1740,72 @@
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
     </row>
-    <row r="6" ht="17" customHeight="1">
-      <c r="A6" t="s" s="13">
-        <v>4</v>
+    <row r="6" ht="17" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="13" t="s">
+        <v>3</v>
       </c>
       <c r="B6" s="14"/>
       <c r="C6" s="14"/>
       <c r="D6" s="15"/>
-      <c r="E6" t="s" s="13">
-        <v>5</v>
+      <c r="E6" s="13" t="s">
+        <v>4</v>
       </c>
       <c r="F6" s="14"/>
       <c r="G6" s="14"/>
     </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="s" s="16">
-        <v>6</v>
+    <row r="7" ht="15" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="16" t="s">
+        <v>5</v>
       </c>
       <c r="B7" s="17"/>
       <c r="C7" s="17"/>
       <c r="D7" s="15"/>
-      <c r="E7" t="s" s="16">
-        <v>7</v>
+      <c r="E7" s="16" t="s">
+        <v>6</v>
       </c>
       <c r="F7" s="17"/>
       <c r="G7" s="17"/>
     </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" t="s" s="16">
-        <v>8</v>
+    <row r="8" ht="15" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="16" t="s">
+        <v>7</v>
       </c>
       <c r="B8" s="17"/>
       <c r="C8" s="17"/>
       <c r="D8" s="15"/>
-      <c r="E8" t="s" s="16">
-        <v>9</v>
+      <c r="E8" s="16" t="s">
+        <v>8</v>
       </c>
       <c r="F8" s="17"/>
       <c r="G8" s="17"/>
     </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" t="s" s="16">
-        <v>10</v>
+    <row r="9" ht="15" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="16" t="s">
+        <v>9</v>
       </c>
       <c r="B9" s="17"/>
       <c r="C9" s="17"/>
       <c r="D9" s="15"/>
-      <c r="E9" t="s" s="16">
-        <v>11</v>
+      <c r="E9" s="16" t="s">
+        <v>10</v>
       </c>
       <c r="F9" s="17"/>
       <c r="G9" s="17"/>
     </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="s" s="16">
-        <v>12</v>
+    <row r="10" ht="15" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="16" t="s">
+        <v>11</v>
       </c>
       <c r="B10" s="17"/>
       <c r="C10" s="17"/>
       <c r="D10" s="15"/>
-      <c r="E10" t="s" s="16">
-        <v>13</v>
+      <c r="E10" s="16" t="s">
+        <v>12</v>
       </c>
       <c r="F10" s="17"/>
       <c r="G10" s="17"/>
     </row>
-    <row r="11" ht="13.55" customHeight="1">
+    <row r="11" ht="13.55" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="12"/>
       <c r="B11" s="12"/>
       <c r="C11" s="12"/>
@@ -1825,192 +1814,192 @@
       <c r="F11" s="12"/>
       <c r="G11" s="12"/>
     </row>
-    <row r="12" ht="24" customHeight="1">
-      <c r="A12" t="s" s="18">
+    <row r="12" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="B12" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="B12" t="s" s="18">
+      <c r="C12" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="C12" t="s" s="18">
+      <c r="D12" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="D12" t="s" s="18">
+      <c r="E12" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="E12" t="s" s="18">
+      <c r="F12" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="F12" t="s" s="18">
+      <c r="G12" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="G12" t="s" s="18">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="13" ht="22" customHeight="1">
+    </row>
+    <row r="13" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="19">
         <v>1</v>
       </c>
-      <c r="B13" t="s" s="20">
+      <c r="B13" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="C13" s="20" t="s">
         <v>21</v>
-      </c>
-      <c r="C13" t="s" s="20">
-        <v>22</v>
       </c>
       <c r="D13" s="21">
         <v>1</v>
       </c>
-      <c r="E13" t="s" s="22">
-        <v>23</v>
+      <c r="E13" s="22" t="s">
+        <v>22</v>
       </c>
       <c r="F13" s="23">
         <v>65000</v>
       </c>
-      <c r="G13" s="23" cm="1">
+      <c r="G13" s="23">
         <f t="array" ref="G13">D13*F13</f>
         <v>65000</v>
       </c>
     </row>
-    <row r="14" ht="22" customHeight="1">
+    <row r="14" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="24">
         <v>2</v>
       </c>
-      <c r="B14" t="s" s="25">
+      <c r="B14" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="C14" s="25" t="s">
         <v>24</v>
-      </c>
-      <c r="C14" t="s" s="25">
-        <v>25</v>
       </c>
       <c r="D14" s="26">
         <v>1</v>
       </c>
-      <c r="E14" t="s" s="27">
-        <v>26</v>
+      <c r="E14" s="27" t="s">
+        <v>25</v>
       </c>
       <c r="F14" s="28">
         <v>38000</v>
       </c>
-      <c r="G14" s="28" cm="1">
+      <c r="G14" s="28">
         <f t="array" ref="G14">D14*F14</f>
         <v>38000</v>
       </c>
     </row>
-    <row r="15" ht="22" customHeight="1">
+    <row r="15" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="19">
         <v>3</v>
       </c>
-      <c r="B15" t="s" s="20">
+      <c r="B15" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="C15" s="20" t="s">
         <v>27</v>
-      </c>
-      <c r="C15" t="s" s="20">
-        <v>28</v>
       </c>
       <c r="D15" s="21">
         <v>2</v>
       </c>
-      <c r="E15" t="s" s="22">
-        <v>29</v>
+      <c r="E15" s="22" t="s">
+        <v>28</v>
       </c>
       <c r="F15" s="23">
         <v>15000</v>
       </c>
-      <c r="G15" s="23" cm="1">
+      <c r="G15" s="23">
         <f t="array" ref="G15">D15*F15</f>
         <v>30000</v>
       </c>
     </row>
-    <row r="16" ht="22" customHeight="1">
+    <row r="16" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="24">
         <v>4</v>
       </c>
-      <c r="B16" t="s" s="25">
+      <c r="B16" s="25" t="s">
+        <v>29</v>
+      </c>
+      <c r="C16" s="25" t="s">
         <v>30</v>
-      </c>
-      <c r="C16" t="s" s="25">
-        <v>31</v>
       </c>
       <c r="D16" s="26">
         <v>1</v>
       </c>
-      <c r="E16" t="s" s="27">
-        <v>32</v>
+      <c r="E16" s="27" t="s">
+        <v>31</v>
       </c>
       <c r="F16" s="28">
         <v>12000</v>
       </c>
-      <c r="G16" s="28" cm="1">
+      <c r="G16" s="28">
         <f t="array" ref="G16">D16*F16</f>
         <v>12000</v>
       </c>
     </row>
-    <row r="17" ht="22" customHeight="1">
+    <row r="17" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="19">
         <v>5</v>
       </c>
-      <c r="B17" t="s" s="20">
+      <c r="B17" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="C17" s="20" t="s">
         <v>33</v>
-      </c>
-      <c r="C17" t="s" s="20">
-        <v>34</v>
       </c>
       <c r="D17" s="21">
         <v>12</v>
       </c>
-      <c r="E17" t="s" s="22">
-        <v>35</v>
+      <c r="E17" s="22" t="s">
+        <v>34</v>
       </c>
       <c r="F17" s="23">
         <v>3000</v>
       </c>
-      <c r="G17" s="23" cm="1">
+      <c r="G17" s="23">
         <f t="array" ref="G17">D17*F17</f>
         <v>36000</v>
       </c>
     </row>
-    <row r="18" ht="17" customHeight="1">
-      <c r="A18" t="s" s="29">
-        <v>36</v>
+    <row r="18" ht="17" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" s="29" t="s">
+        <v>35</v>
       </c>
       <c r="B18" s="30"/>
       <c r="C18" s="30"/>
       <c r="D18" s="30"/>
       <c r="E18" s="30"/>
       <c r="F18" s="31"/>
-      <c r="G18" s="32" cm="1">
+      <c r="G18" s="32">
         <f t="array" ref="G18">SUM(G13:G17)</f>
         <v>181000</v>
       </c>
     </row>
-    <row r="19" ht="17" customHeight="1">
-      <c r="A19" t="s" s="29">
-        <v>37</v>
+    <row r="19" ht="17" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" s="29" t="s">
+        <v>36</v>
       </c>
       <c r="B19" s="30"/>
       <c r="C19" s="30"/>
       <c r="D19" s="30"/>
       <c r="E19" s="30"/>
       <c r="F19" s="31"/>
-      <c r="G19" s="32" cm="1">
+      <c r="G19" s="32">
         <f t="array" ref="G19">ROUND(G18*0.05,0)</f>
         <v>9050</v>
       </c>
     </row>
-    <row r="20" ht="19" customHeight="1">
-      <c r="A20" t="s" s="33">
-        <v>38</v>
+    <row r="20" ht="19" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" s="33" t="s">
+        <v>37</v>
       </c>
       <c r="B20" s="34"/>
       <c r="C20" s="34"/>
       <c r="D20" s="34"/>
       <c r="E20" s="34"/>
       <c r="F20" s="35"/>
-      <c r="G20" s="36" cm="1">
+      <c r="G20" s="36">
         <f t="array" ref="G20">G18+G19</f>
         <v>190050</v>
       </c>
     </row>
-    <row r="21" ht="13.55" customHeight="1">
+    <row r="21" ht="13.55" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="37"/>
       <c r="B21" s="37"/>
       <c r="C21" s="37"/>
@@ -2019,9 +2008,9 @@
       <c r="F21" s="37"/>
       <c r="G21" s="37"/>
     </row>
-    <row r="22" ht="17" customHeight="1">
-      <c r="A22" t="s" s="38">
-        <v>39</v>
+    <row r="22" ht="17" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22" s="38" t="s">
+        <v>38</v>
       </c>
       <c r="B22" s="39"/>
       <c r="C22" s="39"/>
@@ -2030,9 +2019,9 @@
       <c r="F22" s="39"/>
       <c r="G22" s="39"/>
     </row>
-    <row r="23" ht="15" customHeight="1">
-      <c r="A23" t="s" s="40">
-        <v>40</v>
+    <row r="23" ht="15" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" s="40" t="s">
+        <v>39</v>
       </c>
       <c r="B23" s="41"/>
       <c r="C23" s="41"/>
@@ -2041,9 +2030,9 @@
       <c r="F23" s="41"/>
       <c r="G23" s="41"/>
     </row>
-    <row r="24" ht="15" customHeight="1">
-      <c r="A24" t="s" s="40">
-        <v>41</v>
+    <row r="24" ht="15" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" s="40" t="s">
+        <v>40</v>
       </c>
       <c r="B24" s="41"/>
       <c r="C24" s="41"/>
@@ -2052,9 +2041,9 @@
       <c r="F24" s="41"/>
       <c r="G24" s="41"/>
     </row>
-    <row r="25" ht="15" customHeight="1">
-      <c r="A25" t="s" s="40">
-        <v>42</v>
+    <row r="25" ht="15" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25" s="40" t="s">
+        <v>41</v>
       </c>
       <c r="B25" s="41"/>
       <c r="C25" s="41"/>
@@ -2063,7 +2052,7 @@
       <c r="F25" s="41"/>
       <c r="G25" s="41"/>
     </row>
-    <row r="26" ht="13.55" customHeight="1">
+    <row r="26" ht="13.55" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="2"/>
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
@@ -2072,49 +2061,49 @@
       <c r="F26" s="2"/>
       <c r="G26" s="2"/>
     </row>
-    <row r="27" ht="15" customHeight="1">
-      <c r="A27" t="s" s="42">
-        <v>43</v>
+    <row r="27" ht="15" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A27" s="42" t="s">
+        <v>42</v>
       </c>
       <c r="B27" s="43"/>
       <c r="C27" s="43"/>
       <c r="D27" s="15"/>
-      <c r="E27" t="s" s="42">
-        <v>44</v>
+      <c r="E27" s="42" t="s">
+        <v>43</v>
       </c>
       <c r="F27" s="43"/>
       <c r="G27" s="43"/>
     </row>
-    <row r="28" ht="13.55" customHeight="1">
-      <c r="A28" t="s" s="45">
+    <row r="28" ht="13.55" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A28" s="44" t="s">
+        <v>44</v>
+      </c>
+      <c r="B28" s="45"/>
+      <c r="C28" s="45"/>
+      <c r="D28" s="15"/>
+      <c r="E28" s="44" t="s">
         <v>45</v>
       </c>
-      <c r="B28" s="46"/>
-      <c r="C28" s="46"/>
-      <c r="D28" s="15"/>
-      <c r="E28" t="s" s="45">
-        <v>46</v>
-      </c>
-      <c r="F28" s="46"/>
-      <c r="G28" s="46"/>
-    </row>
-    <row r="29" ht="13.55" customHeight="1">
-      <c r="A29" s="46"/>
-      <c r="B29" s="46"/>
-      <c r="C29" s="46"/>
+      <c r="F28" s="45"/>
+      <c r="G28" s="45"/>
+    </row>
+    <row r="29" ht="13.55" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A29" s="45"/>
+      <c r="B29" s="45"/>
+      <c r="C29" s="45"/>
       <c r="D29" s="15"/>
-      <c r="E29" s="46"/>
-      <c r="F29" s="46"/>
-      <c r="G29" s="46"/>
-    </row>
-    <row r="30" ht="19.85" customHeight="1">
-      <c r="A30" s="46"/>
-      <c r="B30" s="46"/>
-      <c r="C30" s="46"/>
+      <c r="E29" s="45"/>
+      <c r="F29" s="45"/>
+      <c r="G29" s="45"/>
+    </row>
+    <row r="30" ht="19.85" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A30" s="45"/>
+      <c r="B30" s="45"/>
+      <c r="C30" s="45"/>
       <c r="D30" s="15"/>
-      <c r="E30" s="46"/>
-      <c r="F30" s="46"/>
-      <c r="G30" s="46"/>
+      <c r="E30" s="45"/>
+      <c r="F30" s="45"/>
+      <c r="G30" s="45"/>
     </row>
   </sheetData>
   <mergeCells count="25">
@@ -2145,9 +2134,10 @@
     <mergeCell ref="E28:G30"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup firstPageNumber="1" fitToHeight="1" fitToWidth="1" scale="100" useFirstPageNumber="0" orientation="portrait" pageOrder="downThenOver"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
   <headerFooter>
     <oddFooter>&amp;C&amp;"Helvetica Neue,Regular"&amp;12&amp;K000000&amp;P</oddFooter>
   </headerFooter>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/AIFirst實作課程/第1個app/商務報價單範本.xlsx
+++ b/AIFirst實作課程/第1個app/商務報價單範本.xlsx
@@ -1,20 +1,43 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <bookViews>
     <workbookView xWindow="0" yWindow="40" windowWidth="15960" windowHeight="18080"/>
   </bookViews>
   <sheets>
-    <sheet sheetId="1" name="商務報價單" state="visible" r:id="rId4"/>
+    <sheet name="商務報價單" sheetId="1" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="47">
+  <si>
+    <t>❖
+{{COMPANY_LOGO | ACME CORP 智慧科技}}</t>
+  </si>
   <si>
     <t>商 務 報 價 單  /  QUOTATION</t>
   </si>
@@ -161,91 +184,95 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="&quot;NT&quot;[$&quot;NT$&quot;]&quot; &quot;#,##0"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="2">
+    <numFmt numFmtId="0" formatCode="General"/>
+    <numFmt numFmtId="59" formatCode="&quot;NT&quot;[$&quot;NT$&quot;]&quot; &quot;#,##0"/>
   </numFmts>
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="17">
     <font>
-      <color theme="1"/>
-      <family val="2"/>
-      <scheme val="minor"/>
       <sz val="11"/>
+      <color indexed="8"/>
       <name val="Calibri"/>
     </font>
     <font>
+      <sz val="12"/>
       <color indexed="8"/>
-      <sz val="11"/>
+      <name val="Helvetica Neue"/>
+    </font>
+    <font>
+      <sz val="15"/>
+      <color indexed="8"/>
       <name val="Calibri"/>
     </font>
     <font>
+      <sz val="12"/>
       <color indexed="11"/>
-      <sz val="12"/>
       <name val="Microsoft JhengHei"/>
     </font>
     <font>
+      <sz val="18"/>
       <color indexed="13"/>
-      <sz val="18"/>
       <name val="Microsoft JhengHei"/>
     </font>
     <font>
+      <sz val="10"/>
       <color indexed="15"/>
-      <sz val="10"/>
       <name val="Microsoft JhengHei"/>
     </font>
     <font>
+      <sz val="10"/>
       <color indexed="16"/>
-      <sz val="10"/>
       <name val="Microsoft JhengHei"/>
     </font>
     <font>
+      <sz val="10"/>
       <color indexed="11"/>
-      <sz val="10"/>
       <name val="Microsoft JhengHei"/>
     </font>
     <font>
+      <sz val="9"/>
       <color indexed="16"/>
-      <sz val="9"/>
       <name val="Microsoft JhengHei"/>
     </font>
     <font>
+      <sz val="10"/>
       <color indexed="14"/>
-      <sz val="10"/>
       <name val="Microsoft JhengHei"/>
     </font>
     <font>
+      <sz val="9"/>
       <color indexed="8"/>
-      <sz val="9"/>
       <name val="Microsoft JhengHei"/>
     </font>
     <font>
+      <sz val="10"/>
       <color indexed="8"/>
-      <sz val="10"/>
       <name val="Microsoft JhengHei"/>
     </font>
     <font>
+      <sz val="11"/>
       <color indexed="13"/>
-      <sz val="11"/>
       <name val="Microsoft JhengHei"/>
     </font>
     <font>
+      <sz val="12"/>
       <color indexed="19"/>
-      <sz val="12"/>
       <name val="Microsoft JhengHei"/>
     </font>
     <font>
+      <sz val="9"/>
       <color indexed="15"/>
-      <sz val="9"/>
       <name val="Microsoft JhengHei"/>
     </font>
     <font>
+      <sz val="9"/>
       <color indexed="20"/>
-      <sz val="9"/>
       <name val="Microsoft JhengHei"/>
     </font>
     <font>
+      <sz val="8"/>
       <color indexed="21"/>
-      <sz val="8"/>
       <name val="Microsoft JhengHei"/>
     </font>
   </fonts>
@@ -259,26 +286,31 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor indexed="12"/>
+        <bgColor auto="1"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor indexed="14"/>
+        <bgColor auto="1"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor indexed="17"/>
+        <bgColor auto="1"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor indexed="11"/>
+        <bgColor auto="1"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor indexed="18"/>
+        <bgColor auto="1"/>
       </patternFill>
     </fill>
   </fills>
@@ -412,143 +444,150 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="46">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+  <cellXfs count="47">
+    <xf numFmtId="0" fontId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" borderId="1" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" borderId="2" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="4" fillId="3" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="3" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="6" fillId="3" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" borderId="5" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="7" fillId="4" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="3" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" borderId="6" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="8" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" borderId="3" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="49" fontId="8" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="9" fillId="5" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="9" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="10" fillId="3" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="9" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="10" fillId="3" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="9" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="10" fillId="3" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="59" fontId="10" fillId="3" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="9" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="10" fillId="6" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="9" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="10" fillId="6" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="9" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="10" fillId="6" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="59" fontId="10" fillId="6" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="8" fillId="3" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="3" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" borderId="3" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="59" fontId="11" fillId="3" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="12" fillId="4" borderId="7" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="7" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="59" fontId="13" fillId="4" borderId="7" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" borderId="8" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="7" borderId="2" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" borderId="2" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="14" borderId="2" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" borderId="2" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="49" fontId="14" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="15" fillId="6" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="3" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="15" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="16" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="49" fontId="16" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="bottom" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" borderId="3" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
   </cellXfs>
@@ -556,65 +595,34 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <tableStyles count="0"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="ff000000"/>
+      <rgbColor rgb="ffffffff"/>
+      <rgbColor rgb="ffff0000"/>
+      <rgbColor rgb="ff00ff00"/>
+      <rgbColor rgb="ff0000ff"/>
+      <rgbColor rgb="ffffff00"/>
+      <rgbColor rgb="ffff00ff"/>
+      <rgbColor rgb="ff00ffff"/>
+      <rgbColor rgb="ff000000"/>
+      <rgbColor rgb="ffaaaaaa"/>
+      <rgbColor rgb="ffcbd5e1"/>
+      <rgbColor rgb="ff1e293b"/>
+      <rgbColor rgb="fff1f5f9"/>
+      <rgbColor rgb="ff0f172a"/>
+      <rgbColor rgb="ffffffff"/>
+      <rgbColor rgb="ff64748b"/>
+      <rgbColor rgb="ff334155"/>
+      <rgbColor rgb="ffe2e8f0"/>
+      <rgbColor rgb="fff8fafc"/>
+      <rgbColor rgb="ff1e3a8a"/>
+      <rgbColor rgb="ff475569"/>
+      <rgbColor rgb="ff94a3b8"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>12000</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>40499</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>187000</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>144500</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="1" name="Picture 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1672,12 +1680,12 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G30"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="8.83333"/>
+  <sheetFormatPr defaultColWidth="8.83333" defaultRowHeight="15" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="8" style="1" customWidth="1"/>
     <col min="2" max="2" width="22" style="1" customWidth="1"/>
@@ -1689,7 +1697,7 @@
     <col min="8" max="16384" width="8.85156" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="13.55" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" ht="13.55" customHeight="1">
       <c r="A1" s="2"/>
       <c r="B1" s="2"/>
       <c r="C1" s="3"/>
@@ -1698,40 +1706,42 @@
       <c r="F1" s="3"/>
       <c r="G1" s="3"/>
     </row>
-    <row r="2" ht="27" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="4"/>
+    <row r="2" ht="27" customHeight="1">
+      <c r="A2" t="s" s="4">
+        <v>0</v>
+      </c>
       <c r="B2" s="5"/>
-      <c r="C2" s="6" t="s">
-        <v>0</v>
+      <c r="C2" t="s" s="6">
+        <v>1</v>
       </c>
       <c r="D2" s="7"/>
       <c r="E2" s="7"/>
       <c r="F2" s="7"/>
       <c r="G2" s="7"/>
     </row>
-    <row r="3" ht="17" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" ht="17" customHeight="1">
       <c r="A3" s="5"/>
       <c r="B3" s="5"/>
-      <c r="C3" s="8" t="s">
-        <v>1</v>
+      <c r="C3" t="s" s="8">
+        <v>2</v>
       </c>
       <c r="D3" s="9"/>
       <c r="E3" s="9"/>
       <c r="F3" s="9"/>
       <c r="G3" s="9"/>
     </row>
-    <row r="4" ht="17" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" ht="17" customHeight="1">
       <c r="A4" s="5"/>
       <c r="B4" s="5"/>
-      <c r="C4" s="10" t="s">
-        <v>2</v>
+      <c r="C4" t="s" s="10">
+        <v>3</v>
       </c>
       <c r="D4" s="11"/>
       <c r="E4" s="11"/>
       <c r="F4" s="11"/>
       <c r="G4" s="11"/>
     </row>
-    <row r="5" ht="13.55" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" ht="13.55" customHeight="1">
       <c r="A5" s="12"/>
       <c r="B5" s="12"/>
       <c r="C5" s="2"/>
@@ -1740,72 +1750,72 @@
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
     </row>
-    <row r="6" ht="17" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="13" t="s">
-        <v>3</v>
+    <row r="6" ht="17" customHeight="1">
+      <c r="A6" t="s" s="13">
+        <v>4</v>
       </c>
       <c r="B6" s="14"/>
       <c r="C6" s="14"/>
       <c r="D6" s="15"/>
-      <c r="E6" s="13" t="s">
-        <v>4</v>
+      <c r="E6" t="s" s="13">
+        <v>5</v>
       </c>
       <c r="F6" s="14"/>
       <c r="G6" s="14"/>
     </row>
-    <row r="7" ht="15" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="16" t="s">
-        <v>5</v>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="s" s="16">
+        <v>6</v>
       </c>
       <c r="B7" s="17"/>
       <c r="C7" s="17"/>
       <c r="D7" s="15"/>
-      <c r="E7" s="16" t="s">
-        <v>6</v>
+      <c r="E7" t="s" s="16">
+        <v>7</v>
       </c>
       <c r="F7" s="17"/>
       <c r="G7" s="17"/>
     </row>
-    <row r="8" ht="15" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="16" t="s">
-        <v>7</v>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" t="s" s="16">
+        <v>8</v>
       </c>
       <c r="B8" s="17"/>
       <c r="C8" s="17"/>
       <c r="D8" s="15"/>
-      <c r="E8" s="16" t="s">
-        <v>8</v>
+      <c r="E8" t="s" s="16">
+        <v>9</v>
       </c>
       <c r="F8" s="17"/>
       <c r="G8" s="17"/>
     </row>
-    <row r="9" ht="15" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="16" t="s">
-        <v>9</v>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" t="s" s="16">
+        <v>10</v>
       </c>
       <c r="B9" s="17"/>
       <c r="C9" s="17"/>
       <c r="D9" s="15"/>
-      <c r="E9" s="16" t="s">
-        <v>10</v>
+      <c r="E9" t="s" s="16">
+        <v>11</v>
       </c>
       <c r="F9" s="17"/>
       <c r="G9" s="17"/>
     </row>
-    <row r="10" ht="15" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="16" t="s">
-        <v>11</v>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="s" s="16">
+        <v>12</v>
       </c>
       <c r="B10" s="17"/>
       <c r="C10" s="17"/>
       <c r="D10" s="15"/>
-      <c r="E10" s="16" t="s">
-        <v>12</v>
+      <c r="E10" t="s" s="16">
+        <v>13</v>
       </c>
       <c r="F10" s="17"/>
       <c r="G10" s="17"/>
     </row>
-    <row r="11" ht="13.55" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" ht="13.55" customHeight="1">
       <c r="A11" s="12"/>
       <c r="B11" s="12"/>
       <c r="C11" s="12"/>
@@ -1814,192 +1824,192 @@
       <c r="F11" s="12"/>
       <c r="G11" s="12"/>
     </row>
-    <row r="12" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="B12" s="18" t="s">
+    <row r="12" ht="24" customHeight="1">
+      <c r="A12" t="s" s="18">
         <v>14</v>
       </c>
-      <c r="C12" s="18" t="s">
+      <c r="B12" t="s" s="18">
         <v>15</v>
       </c>
-      <c r="D12" s="18" t="s">
+      <c r="C12" t="s" s="18">
         <v>16</v>
       </c>
-      <c r="E12" s="18" t="s">
+      <c r="D12" t="s" s="18">
         <v>17</v>
       </c>
-      <c r="F12" s="18" t="s">
+      <c r="E12" t="s" s="18">
         <v>18</v>
       </c>
-      <c r="G12" s="18" t="s">
+      <c r="F12" t="s" s="18">
         <v>19</v>
       </c>
-    </row>
-    <row r="13" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G12" t="s" s="18">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" ht="22" customHeight="1">
       <c r="A13" s="19">
         <v>1</v>
       </c>
-      <c r="B13" s="20" t="s">
-        <v>20</v>
-      </c>
-      <c r="C13" s="20" t="s">
+      <c r="B13" t="s" s="20">
         <v>21</v>
+      </c>
+      <c r="C13" t="s" s="20">
+        <v>22</v>
       </c>
       <c r="D13" s="21">
         <v>1</v>
       </c>
-      <c r="E13" s="22" t="s">
-        <v>22</v>
+      <c r="E13" t="s" s="22">
+        <v>23</v>
       </c>
       <c r="F13" s="23">
         <v>65000</v>
       </c>
-      <c r="G13" s="23">
+      <c r="G13" s="23" cm="1">
         <f t="array" ref="G13">D13*F13</f>
         <v>65000</v>
       </c>
     </row>
-    <row r="14" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" ht="22" customHeight="1">
       <c r="A14" s="24">
         <v>2</v>
       </c>
-      <c r="B14" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="C14" s="25" t="s">
+      <c r="B14" t="s" s="25">
         <v>24</v>
+      </c>
+      <c r="C14" t="s" s="25">
+        <v>25</v>
       </c>
       <c r="D14" s="26">
         <v>1</v>
       </c>
-      <c r="E14" s="27" t="s">
-        <v>25</v>
+      <c r="E14" t="s" s="27">
+        <v>26</v>
       </c>
       <c r="F14" s="28">
         <v>38000</v>
       </c>
-      <c r="G14" s="28">
+      <c r="G14" s="28" cm="1">
         <f t="array" ref="G14">D14*F14</f>
         <v>38000</v>
       </c>
     </row>
-    <row r="15" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" ht="22" customHeight="1">
       <c r="A15" s="19">
         <v>3</v>
       </c>
-      <c r="B15" s="20" t="s">
-        <v>26</v>
-      </c>
-      <c r="C15" s="20" t="s">
+      <c r="B15" t="s" s="20">
         <v>27</v>
+      </c>
+      <c r="C15" t="s" s="20">
+        <v>28</v>
       </c>
       <c r="D15" s="21">
         <v>2</v>
       </c>
-      <c r="E15" s="22" t="s">
-        <v>28</v>
+      <c r="E15" t="s" s="22">
+        <v>29</v>
       </c>
       <c r="F15" s="23">
         <v>15000</v>
       </c>
-      <c r="G15" s="23">
+      <c r="G15" s="23" cm="1">
         <f t="array" ref="G15">D15*F15</f>
         <v>30000</v>
       </c>
     </row>
-    <row r="16" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" ht="22" customHeight="1">
       <c r="A16" s="24">
         <v>4</v>
       </c>
-      <c r="B16" s="25" t="s">
-        <v>29</v>
-      </c>
-      <c r="C16" s="25" t="s">
+      <c r="B16" t="s" s="25">
         <v>30</v>
+      </c>
+      <c r="C16" t="s" s="25">
+        <v>31</v>
       </c>
       <c r="D16" s="26">
         <v>1</v>
       </c>
-      <c r="E16" s="27" t="s">
-        <v>31</v>
+      <c r="E16" t="s" s="27">
+        <v>32</v>
       </c>
       <c r="F16" s="28">
         <v>12000</v>
       </c>
-      <c r="G16" s="28">
+      <c r="G16" s="28" cm="1">
         <f t="array" ref="G16">D16*F16</f>
         <v>12000</v>
       </c>
     </row>
-    <row r="17" ht="22" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" ht="22" customHeight="1">
       <c r="A17" s="19">
         <v>5</v>
       </c>
-      <c r="B17" s="20" t="s">
-        <v>32</v>
-      </c>
-      <c r="C17" s="20" t="s">
+      <c r="B17" t="s" s="20">
         <v>33</v>
+      </c>
+      <c r="C17" t="s" s="20">
+        <v>34</v>
       </c>
       <c r="D17" s="21">
         <v>12</v>
       </c>
-      <c r="E17" s="22" t="s">
-        <v>34</v>
+      <c r="E17" t="s" s="22">
+        <v>35</v>
       </c>
       <c r="F17" s="23">
         <v>3000</v>
       </c>
-      <c r="G17" s="23">
+      <c r="G17" s="23" cm="1">
         <f t="array" ref="G17">D17*F17</f>
         <v>36000</v>
       </c>
     </row>
-    <row r="18" ht="17" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="29" t="s">
-        <v>35</v>
+    <row r="18" ht="17" customHeight="1">
+      <c r="A18" t="s" s="29">
+        <v>36</v>
       </c>
       <c r="B18" s="30"/>
       <c r="C18" s="30"/>
       <c r="D18" s="30"/>
       <c r="E18" s="30"/>
       <c r="F18" s="31"/>
-      <c r="G18" s="32">
+      <c r="G18" s="32" cm="1">
         <f t="array" ref="G18">SUM(G13:G17)</f>
         <v>181000</v>
       </c>
     </row>
-    <row r="19" ht="17" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="29" t="s">
-        <v>36</v>
+    <row r="19" ht="17" customHeight="1">
+      <c r="A19" t="s" s="29">
+        <v>37</v>
       </c>
       <c r="B19" s="30"/>
       <c r="C19" s="30"/>
       <c r="D19" s="30"/>
       <c r="E19" s="30"/>
       <c r="F19" s="31"/>
-      <c r="G19" s="32">
+      <c r="G19" s="32" cm="1">
         <f t="array" ref="G19">ROUND(G18*0.05,0)</f>
         <v>9050</v>
       </c>
     </row>
-    <row r="20" ht="19" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="33" t="s">
-        <v>37</v>
+    <row r="20" ht="19" customHeight="1">
+      <c r="A20" t="s" s="33">
+        <v>38</v>
       </c>
       <c r="B20" s="34"/>
       <c r="C20" s="34"/>
       <c r="D20" s="34"/>
       <c r="E20" s="34"/>
       <c r="F20" s="35"/>
-      <c r="G20" s="36">
+      <c r="G20" s="36" cm="1">
         <f t="array" ref="G20">G18+G19</f>
         <v>190050</v>
       </c>
     </row>
-    <row r="21" ht="13.55" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" ht="13.55" customHeight="1">
       <c r="A21" s="37"/>
       <c r="B21" s="37"/>
       <c r="C21" s="37"/>
@@ -2008,9 +2018,9 @@
       <c r="F21" s="37"/>
       <c r="G21" s="37"/>
     </row>
-    <row r="22" ht="17" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="38" t="s">
-        <v>38</v>
+    <row r="22" ht="17" customHeight="1">
+      <c r="A22" t="s" s="38">
+        <v>39</v>
       </c>
       <c r="B22" s="39"/>
       <c r="C22" s="39"/>
@@ -2019,9 +2029,9 @@
       <c r="F22" s="39"/>
       <c r="G22" s="39"/>
     </row>
-    <row r="23" ht="15" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="40" t="s">
-        <v>39</v>
+    <row r="23" ht="15" customHeight="1">
+      <c r="A23" t="s" s="40">
+        <v>40</v>
       </c>
       <c r="B23" s="41"/>
       <c r="C23" s="41"/>
@@ -2030,9 +2040,9 @@
       <c r="F23" s="41"/>
       <c r="G23" s="41"/>
     </row>
-    <row r="24" ht="15" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="40" t="s">
-        <v>40</v>
+    <row r="24" ht="15" customHeight="1">
+      <c r="A24" t="s" s="40">
+        <v>41</v>
       </c>
       <c r="B24" s="41"/>
       <c r="C24" s="41"/>
@@ -2041,9 +2051,9 @@
       <c r="F24" s="41"/>
       <c r="G24" s="41"/>
     </row>
-    <row r="25" ht="15" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="40" t="s">
-        <v>41</v>
+    <row r="25" ht="15" customHeight="1">
+      <c r="A25" t="s" s="40">
+        <v>42</v>
       </c>
       <c r="B25" s="41"/>
       <c r="C25" s="41"/>
@@ -2052,7 +2062,7 @@
       <c r="F25" s="41"/>
       <c r="G25" s="41"/>
     </row>
-    <row r="26" ht="13.55" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="26" ht="13.55" customHeight="1">
       <c r="A26" s="2"/>
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
@@ -2061,49 +2071,49 @@
       <c r="F26" s="2"/>
       <c r="G26" s="2"/>
     </row>
-    <row r="27" ht="15" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" s="42" t="s">
-        <v>42</v>
+    <row r="27" ht="15" customHeight="1">
+      <c r="A27" t="s" s="42">
+        <v>43</v>
       </c>
       <c r="B27" s="43"/>
       <c r="C27" s="43"/>
       <c r="D27" s="15"/>
-      <c r="E27" s="42" t="s">
-        <v>43</v>
+      <c r="E27" t="s" s="42">
+        <v>44</v>
       </c>
       <c r="F27" s="43"/>
       <c r="G27" s="43"/>
     </row>
-    <row r="28" ht="13.55" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" s="44" t="s">
-        <v>44</v>
-      </c>
-      <c r="B28" s="45"/>
-      <c r="C28" s="45"/>
+    <row r="28" ht="13.55" customHeight="1">
+      <c r="A28" t="s" s="45">
+        <v>45</v>
+      </c>
+      <c r="B28" s="46"/>
+      <c r="C28" s="46"/>
       <c r="D28" s="15"/>
-      <c r="E28" s="44" t="s">
-        <v>45</v>
-      </c>
-      <c r="F28" s="45"/>
-      <c r="G28" s="45"/>
-    </row>
-    <row r="29" ht="13.55" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="45"/>
-      <c r="B29" s="45"/>
-      <c r="C29" s="45"/>
+      <c r="E28" t="s" s="45">
+        <v>46</v>
+      </c>
+      <c r="F28" s="46"/>
+      <c r="G28" s="46"/>
+    </row>
+    <row r="29" ht="13.55" customHeight="1">
+      <c r="A29" s="46"/>
+      <c r="B29" s="46"/>
+      <c r="C29" s="46"/>
       <c r="D29" s="15"/>
-      <c r="E29" s="45"/>
-      <c r="F29" s="45"/>
-      <c r="G29" s="45"/>
-    </row>
-    <row r="30" ht="19.85" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" s="45"/>
-      <c r="B30" s="45"/>
-      <c r="C30" s="45"/>
+      <c r="E29" s="46"/>
+      <c r="F29" s="46"/>
+      <c r="G29" s="46"/>
+    </row>
+    <row r="30" ht="19.85" customHeight="1">
+      <c r="A30" s="46"/>
+      <c r="B30" s="46"/>
+      <c r="C30" s="46"/>
       <c r="D30" s="15"/>
-      <c r="E30" s="45"/>
-      <c r="F30" s="45"/>
-      <c r="G30" s="45"/>
+      <c r="E30" s="46"/>
+      <c r="F30" s="46"/>
+      <c r="G30" s="46"/>
     </row>
   </sheetData>
   <mergeCells count="25">
@@ -2134,10 +2144,9 @@
     <mergeCell ref="E28:G30"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup firstPageNumber="1" fitToHeight="1" fitToWidth="1" scale="100" useFirstPageNumber="0" orientation="portrait" pageOrder="downThenOver"/>
   <headerFooter>
     <oddFooter>&amp;C&amp;"Helvetica Neue,Regular"&amp;12&amp;K000000&amp;P</oddFooter>
   </headerFooter>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>